--- a/photo_links.xlsx
+++ b/photo_links.xlsx
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\001_image_BN-BAG-62-g.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\001_image_BN-BAG-62-g.jpg</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\6977703651713\002_image_6977703651713.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\6977703651713\002_image_6977703651713.jpg</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\002_image_BN-BAG-62-g.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\002_image_BN-BAG-62-g.jpg</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\6977703651713\3_image_6977703651713.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\6977703651713\3_image_6977703651713.jpg</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\3_image_BN-BAG-62-g.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\3_image_BN-BAG-62-g.jpg</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\5_image_BN-BAG-62-g.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\5_image_BN-BAG-62-g.jpg</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\6_image_BN-BAG-62-g.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\6_image_BN-BAG-62-g.jpg</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\7_image_BN-BAG-62-g.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/344/без фоторум\BN-BAG-62-g\7_image_BN-BAG-62-g.jpg</t>
         </is>
       </c>
       <c r="E518" t="n">

--- a/photo_links.xlsx
+++ b/photo_links.xlsx
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39139-1\001_image_BV39139-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39139-1\001_image_BV39139-1.jpg</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\1_image_BV39223-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\1_image_BV39223-1.jpg</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\1_image_BV39318-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\1_image_BV39318-1.jpg</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\1_image_BV39351-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\1_image_BV39351-1.jpg</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-1\1_image_BV39529-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-1\1_image_BV39529-1.jpg</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\001_image_DRL1925-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\001_image_DRL1925-1.jpg</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\1_image_L501-041857.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\1_image_L501-041857.jpg</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\1_image_L501-042014.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\1_image_L501-042014.jpg</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\1_image_L501-042021.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\1_image_L501-042021.jpg</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042038\1_image_L501-042038.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042038\1_image_L501-042038.jpg</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\1_image_TW-Bella-black.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\1_image_TW-Bella-black.jpg</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\002_image_5202801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\002_image_5202801.jpg</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\2_image_5204101.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\2_image_5204101.jpg</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\2_image_L501-041857.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\2_image_L501-041857.jpg</t>
         </is>
       </c>
       <c r="E451" t="n">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\2_image_L501-042014.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\2_image_L501-042014.jpg</t>
         </is>
       </c>
       <c r="E452" t="n">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\2_image_L501-042021.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\2_image_L501-042021.jpg</t>
         </is>
       </c>
       <c r="E453" t="n">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042038\2_image_L501-042038.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042038\2_image_L501-042038.jpg</t>
         </is>
       </c>
       <c r="E454" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\2_image_TW-Bella-black.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\2_image_TW-Bella-black.jpg</t>
         </is>
       </c>
       <c r="E522" t="n">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\3_image_5204101.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\3_image_5204101.jpg</t>
         </is>
       </c>
       <c r="E582" t="n">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\3_image_BV39223-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\3_image_BV39223-1.jpg</t>
         </is>
       </c>
       <c r="E613" t="n">
@@ -17630,7 +17630,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\3_image_BV39318-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\3_image_BV39318-1.jpg</t>
         </is>
       </c>
       <c r="E615" t="n">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\3_image_L501-041857.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\3_image_L501-041857.jpg</t>
         </is>
       </c>
       <c r="E683" t="n">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\3_image_L501-042014.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\3_image_L501-042014.jpg</t>
         </is>
       </c>
       <c r="E684" t="n">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\3_image_L501-042021.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\3_image_L501-042021.jpg</t>
         </is>
       </c>
       <c r="E685" t="n">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042038\3_image_L501-042038.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042038\3_image_L501-042038.jpg</t>
         </is>
       </c>
       <c r="E686" t="n">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\3_image_TW-Bella-black.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\3_image_TW-Bella-black.jpg</t>
         </is>
       </c>
       <c r="E750" t="n">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5193401\4_image_5193401.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5193401\4_image_5193401.jpg</t>
         </is>
       </c>
       <c r="E800" t="n">
@@ -22838,7 +22838,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\4_image_5202801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\4_image_5202801.jpg</t>
         </is>
       </c>
       <c r="E801" t="n">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\4_image_5204101.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\4_image_5204101.jpg</t>
         </is>
       </c>
       <c r="E802" t="n">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\4_image_5205801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\4_image_5205801.jpg</t>
         </is>
       </c>
       <c r="E804" t="n">
@@ -23734,7 +23734,7 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39139-1\4_image_BV39139-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39139-1\4_image_BV39139-1.jpg</t>
         </is>
       </c>
       <c r="E833" t="n">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\4_image_BV39223-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\4_image_BV39223-1.jpg</t>
         </is>
       </c>
       <c r="E836" t="n">
@@ -23958,7 +23958,7 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\4_image_BV39318-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\4_image_BV39318-1.jpg</t>
         </is>
       </c>
       <c r="E841" t="n">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-232\4_image_BV39318-232.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-232\4_image_BV39318-232.jpg</t>
         </is>
       </c>
       <c r="E842" t="n">
@@ -24014,7 +24014,7 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-76A\4_image_BV39318-76A.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-76A\4_image_BV39318-76A.jpg</t>
         </is>
       </c>
       <c r="E843" t="n">
@@ -24042,7 +24042,7 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\4_image_BV39351-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\4_image_BV39351-1.jpg</t>
         </is>
       </c>
       <c r="E844" t="n">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-1\4_image_BV39529-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-1\4_image_BV39529-1.jpg</t>
         </is>
       </c>
       <c r="E845" t="n">
@@ -24098,7 +24098,7 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-145\4_image_BV39529-145.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-145\4_image_BV39529-145.jpg</t>
         </is>
       </c>
       <c r="E846" t="n">
@@ -24322,7 +24322,7 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\4_image_DRL1925-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\4_image_DRL1925-1.jpg</t>
         </is>
       </c>
       <c r="E854" t="n">
@@ -26310,7 +26310,7 @@
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\4_image_L501-041857.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\4_image_L501-041857.jpg</t>
         </is>
       </c>
       <c r="E925" t="n">
@@ -26338,7 +26338,7 @@
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\4_image_L501-042014.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\4_image_L501-042014.jpg</t>
         </is>
       </c>
       <c r="E926" t="n">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\4_image_TW-Bella-black.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\4_image_TW-Bella-black.jpg</t>
         </is>
       </c>
       <c r="E993" t="n">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5193401\5_image_5193401.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5193401\5_image_5193401.jpg</t>
         </is>
       </c>
       <c r="E1041" t="n">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\5_image_5202801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\5_image_5202801.jpg</t>
         </is>
       </c>
       <c r="E1042" t="n">
@@ -29614,7 +29614,7 @@
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\5_image_5204101.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\5_image_5204101.jpg</t>
         </is>
       </c>
       <c r="E1043" t="n">
@@ -29642,7 +29642,7 @@
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205701\5_image_5205701.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205701\5_image_5205701.jpg</t>
         </is>
       </c>
       <c r="E1044" t="n">
@@ -29670,7 +29670,7 @@
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\5_image_5205801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\5_image_5205801.jpg</t>
         </is>
       </c>
       <c r="E1045" t="n">
@@ -30650,7 +30650,7 @@
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\5_image_BV39223-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\5_image_BV39223-1.jpg</t>
         </is>
       </c>
       <c r="E1080" t="n">
@@ -30790,7 +30790,7 @@
       </c>
       <c r="D1085" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\5_image_BV39318-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\5_image_BV39318-1.jpg</t>
         </is>
       </c>
       <c r="E1085" t="n">
@@ -30818,7 +30818,7 @@
       </c>
       <c r="D1086" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-232\5_image_BV39318-232.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-232\5_image_BV39318-232.jpg</t>
         </is>
       </c>
       <c r="E1086" t="n">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="D1087" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-76A\5_image_BV39318-76A.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-76A\5_image_BV39318-76A.jpg</t>
         </is>
       </c>
       <c r="E1087" t="n">
@@ -30874,7 +30874,7 @@
       </c>
       <c r="D1088" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\5_image_BV39351-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\5_image_BV39351-1.jpg</t>
         </is>
       </c>
       <c r="E1088" t="n">
@@ -31210,7 +31210,7 @@
       </c>
       <c r="D1100" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\5_image_DRL1925-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\5_image_DRL1925-1.jpg</t>
         </is>
       </c>
       <c r="E1100" t="n">
@@ -33226,7 +33226,7 @@
       </c>
       <c r="D1172" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\5_image_L501-041857.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-041857\5_image_L501-041857.jpg</t>
         </is>
       </c>
       <c r="E1172" t="n">
@@ -35018,7 +35018,7 @@
       </c>
       <c r="D1236" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\5_image_TW-Bella-black.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\TW-Bella-black\5_image_TW-Bella-black.jpg</t>
         </is>
       </c>
       <c r="E1236" t="n">
@@ -35451,7 +35451,7 @@
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>20906_1 (1)</t>
+          <t>20906_1</t>
         </is>
       </c>
       <c r="B1252" t="inlineStr">
@@ -35461,12 +35461,12 @@
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/20906_1 (1)/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/20906_1/006.jpg</t>
         </is>
       </c>
       <c r="D1252" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\20906_1\006_image_20906_1 (1).png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\20906_1\006_image_20906_1.jpg</t>
         </is>
       </c>
       <c r="E1252" t="n">
@@ -36026,7 +36026,7 @@
       </c>
       <c r="D1272" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\6_image_5202801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\6_image_5202801.jpg</t>
         </is>
       </c>
       <c r="E1272" t="n">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="D1273" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\6_image_5204101.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\6_image_5204101.jpg</t>
         </is>
       </c>
       <c r="E1273" t="n">
@@ -36082,7 +36082,7 @@
       </c>
       <c r="D1274" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205701\6_image_5205701.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205701\6_image_5205701.jpg</t>
         </is>
       </c>
       <c r="E1274" t="n">
@@ -36110,7 +36110,7 @@
       </c>
       <c r="D1275" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\6_image_5205801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\6_image_5205801.jpg</t>
         </is>
       </c>
       <c r="E1275" t="n">
@@ -37006,7 +37006,7 @@
       </c>
       <c r="D1307" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\6_image_BV39223-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\6_image_BV39223-1.jpg</t>
         </is>
       </c>
       <c r="E1307" t="n">
@@ -37062,7 +37062,7 @@
       </c>
       <c r="D1309" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-145\6_image_BV39223-145.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-145\6_image_BV39223-145.jpg</t>
         </is>
       </c>
       <c r="E1309" t="n">
@@ -37174,7 +37174,7 @@
       </c>
       <c r="D1313" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-232\6_image_BV39318-232.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-232\6_image_BV39318-232.jpg</t>
         </is>
       </c>
       <c r="E1313" t="n">
@@ -37230,7 +37230,7 @@
       </c>
       <c r="D1315" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\6_image_BV39351-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\6_image_BV39351-1.jpg</t>
         </is>
       </c>
       <c r="E1315" t="n">
@@ -37258,7 +37258,7 @@
       </c>
       <c r="D1316" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-1\6_image_BV39529-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-1\6_image_BV39529-1.jpg</t>
         </is>
       </c>
       <c r="E1316" t="n">
@@ -37286,7 +37286,7 @@
       </c>
       <c r="D1317" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-145\6_image_BV39529-145.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39529-145\6_image_BV39529-145.jpg</t>
         </is>
       </c>
       <c r="E1317" t="n">
@@ -37566,7 +37566,7 @@
       </c>
       <c r="D1327" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\6_image_DRL1925-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\6_image_DRL1925-1.jpg</t>
         </is>
       </c>
       <c r="E1327" t="n">
@@ -39442,7 +39442,7 @@
       </c>
       <c r="D1394" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\6_image_L501-042014.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\6_image_L501-042014.jpg</t>
         </is>
       </c>
       <c r="E1394" t="n">
@@ -41850,7 +41850,7 @@
       </c>
       <c r="D1480" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\7_image_5202801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\7_image_5202801.jpg</t>
         </is>
       </c>
       <c r="E1480" t="n">
@@ -41878,7 +41878,7 @@
       </c>
       <c r="D1481" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\7_image_5204101.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\7_image_5204101.jpg</t>
         </is>
       </c>
       <c r="E1481" t="n">
@@ -42746,7 +42746,7 @@
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39032-191\7_image_BV39032-191.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39032-191\7_image_BV39032-191.jpg</t>
         </is>
       </c>
       <c r="E1512" t="n">
@@ -42858,7 +42858,7 @@
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\7_image_BV39223-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-1\7_image_BV39223-1.jpg</t>
         </is>
       </c>
       <c r="E1516" t="n">
@@ -42914,7 +42914,7 @@
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-145\7_image_BV39223-145.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-145\7_image_BV39223-145.jpg</t>
         </is>
       </c>
       <c r="E1518" t="n">
@@ -42998,7 +42998,7 @@
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\7_image_BV39318-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-1\7_image_BV39318-1.jpg</t>
         </is>
       </c>
       <c r="E1521" t="n">
@@ -43026,7 +43026,7 @@
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-232\7_image_BV39318-232.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-232\7_image_BV39318-232.jpg</t>
         </is>
       </c>
       <c r="E1522" t="n">
@@ -43054,7 +43054,7 @@
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-76A\7_image_BV39318-76A.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39318-76A\7_image_BV39318-76A.jpg</t>
         </is>
       </c>
       <c r="E1523" t="n">
@@ -43082,7 +43082,7 @@
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\7_image_BV39351-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39351-1\7_image_BV39351-1.jpg</t>
         </is>
       </c>
       <c r="E1524" t="n">
@@ -43334,7 +43334,7 @@
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\7_image_DRL1925-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\7_image_DRL1925-1.jpg</t>
         </is>
       </c>
       <c r="E1533" t="n">
@@ -44874,7 +44874,7 @@
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\7_image_L501-042014.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042014\7_image_L501-042014.jpg</t>
         </is>
       </c>
       <c r="E1588" t="n">
@@ -44902,7 +44902,7 @@
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\7_image_L501-042021.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\7_image_L501-042021.jpg</t>
         </is>
       </c>
       <c r="E1589" t="n">
@@ -44930,7 +44930,7 @@
       </c>
       <c r="D1590" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042038\7_image_L501-042038.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042038\7_image_L501-042038.jpg</t>
         </is>
       </c>
       <c r="E1590" t="n">
@@ -46834,7 +46834,7 @@
       </c>
       <c r="D1658" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\8_image_5202801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\8_image_5202801.jpg</t>
         </is>
       </c>
       <c r="E1658" t="n">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="D1659" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\8_image_5204101.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\8_image_5204101.jpg</t>
         </is>
       </c>
       <c r="E1659" t="n">
@@ -47506,7 +47506,7 @@
       </c>
       <c r="D1682" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39139-1\008_image_BV39139-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39139-1\008_image_BV39139-1.jpg</t>
         </is>
       </c>
       <c r="E1682" t="n">
@@ -47590,7 +47590,7 @@
       </c>
       <c r="D1685" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-145\008_image_BV39223-145.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\BV39223-145\008_image_BV39223-145.jpg</t>
         </is>
       </c>
       <c r="E1685" t="n">
@@ -47814,7 +47814,7 @@
       </c>
       <c r="D1693" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\008_image_DRL1925-1.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\DRL1925-1\008_image_DRL1925-1.jpg</t>
         </is>
       </c>
       <c r="E1693" t="n">
@@ -48794,7 +48794,7 @@
       </c>
       <c r="D1728" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\8_image_L501-042021.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\L501-042021\8_image_L501-042021.jpg</t>
         </is>
       </c>
       <c r="E1728" t="n">
@@ -50222,7 +50222,7 @@
       </c>
       <c r="D1779" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5193401\9_image_5193401.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5193401\9_image_5193401.jpg</t>
         </is>
       </c>
       <c r="E1779" t="n">
@@ -50278,7 +50278,7 @@
       </c>
       <c r="D1781" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\9_image_5204101.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5204101\9_image_5204101.jpg</t>
         </is>
       </c>
       <c r="E1781" t="n">
@@ -50306,7 +50306,7 @@
       </c>
       <c r="D1782" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205701\9_image_5205701.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205701\9_image_5205701.jpg</t>
         </is>
       </c>
       <c r="E1782" t="n">
@@ -50334,7 +50334,7 @@
       </c>
       <c r="D1783" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\9_image_5205801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\9_image_5205801.jpg</t>
         </is>
       </c>
       <c r="E1783" t="n">
@@ -52798,7 +52798,7 @@
       </c>
       <c r="D1871" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\10_image_5202801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\10_image_5202801.jpg</t>
         </is>
       </c>
       <c r="E1871" t="n">
@@ -52882,7 +52882,7 @@
       </c>
       <c r="D1874" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\10_image_5205801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\10_image_5205801.jpg</t>
         </is>
       </c>
       <c r="E1874" t="n">
@@ -54646,7 +54646,7 @@
       </c>
       <c r="D1937" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\011_image_5202801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5202801\011_image_5202801.jpg</t>
         </is>
       </c>
       <c r="E1937" t="n">
@@ -54674,7 +54674,7 @@
       </c>
       <c r="D1938" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\011_image_5205801.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/338 фото/338 обрізані\5205801\011_image_5205801.jpg</t>
         </is>
       </c>
       <c r="E1938" t="n">

--- a/photo_links.xlsx
+++ b/photo_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>125V1FX92-BLACK</t>
+          <t>1065618885</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/125V1FX92-BLACK/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1065618885/001.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\125V1FX92-BLACK\1_image_125V1FX92-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\1065618885\001_image_1065618885.jpg</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>734</v>
+        <v>1599</v>
       </c>
       <c r="F2" t="n">
-        <v>578</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>125V1GENAV37-BLACK</t>
+          <t>30311066</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -489,16 +489,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/125V1GENAV37-BLACK/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311066/001.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\125V1GENAV37-BLACK\1_image_125V1GENAV37-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\30311066\001_image_30311066.jpg</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>780</v>
+        <v>989</v>
       </c>
       <c r="F3" t="n">
         <v>515</v>
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>150V1GENAV36-BLACK</t>
+          <t>30311067</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,16 +517,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/150V1GENAV36-BLACK/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311067/001.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\150V1GENAV36-BLACK\1_image_150V1GENAV36-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\30311067\001_image_30311067.jpg</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>740</v>
+        <v>886</v>
       </c>
       <c r="F4" t="n">
         <v>515</v>
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>150VFX85-BLACK</t>
+          <t>30311068</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -545,25 +545,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/150VFX85-BLACK/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311068/001.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\150VFX85-BLACK\1_image_150VFX85-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\30311068\001_image_30311068.jpg</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>739</v>
+        <v>935</v>
       </c>
       <c r="F5" t="n">
-        <v>589</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>31111120</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -573,25 +573,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18010/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/31111120/001.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\18010\1_image_18010.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\31111120\001_image_31111120.jpg</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1123</v>
+        <v>619</v>
       </c>
       <c r="F6" t="n">
-        <v>898</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>31211120</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,25 +601,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18240/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/31211120/001.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\18240\1_image_18240.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\31211120\001_image_31211120.jpg</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1094</v>
+        <v>865</v>
       </c>
       <c r="F7" t="n">
-        <v>860</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BN-BELT-3-RAVEN</t>
+          <t>50223060</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -629,25 +629,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-3-RAVEN/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223060/001.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-3-RAVEN\1_image_BN-BELT-3-RAVEN.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223060\001_image_50223060.jpg</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>612</v>
+        <v>520</v>
       </c>
       <c r="F8" t="n">
-        <v>587</v>
+        <v>718</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BN-BELT-8-RAVEN</t>
+          <t>50223161</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,25 +657,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-8-RAVEN/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223161/001.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-8-RAVEN\1_image_BN-BELT-8-RAVEN.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223161\001_image_50223161.jpg</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>566</v>
+        <v>520</v>
       </c>
       <c r="F9" t="n">
-        <v>569</v>
+        <v>718</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BS70106-01</t>
+          <t>50223401</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -685,25 +685,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BS70106-01/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223401/001.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BS70106-01\1_image_BS70106-01.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223401\001_image_50223401.jpg</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>750</v>
+        <v>520</v>
       </c>
       <c r="F10" t="n">
-        <v>710</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEW-ALN-010</t>
+          <t>50223406</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -713,25 +713,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NEW-ALN-010/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223406/001.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NEW-ALN-010\1_image_NEW-ALN-010.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223406\001_image_50223406.jpg</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>899</v>
+        <v>520</v>
       </c>
       <c r="F11" t="n">
-        <v>566</v>
+        <v>718</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NW-TUR-35K-0014</t>
+          <t>51411101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -741,25 +741,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NW-TUR-35K-0014/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411101/001.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NW-TUR-35K-0014\1_image_NW-TUR-35K-0014.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\001_image_51411101.jpg</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>878</v>
+        <v>520</v>
       </c>
       <c r="F12" t="n">
-        <v>586</v>
+        <v>718</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NW-TUR-35K-0016</t>
+          <t>53400066</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -769,25 +769,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NW-TUR-35K-0016/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400066/001.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NW-TUR-35K-0016\1_image_NW-TUR-35K-0016.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400066\001_image_53400066.jpg</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>889</v>
+        <v>520</v>
       </c>
       <c r="F13" t="n">
-        <v>547</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NWKZ-38MM-KIT-006</t>
+          <t>53400067</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -797,25 +797,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NWKZ-38MM-KIT-006/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400067/001.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NWKZ-38MM-KIT-006\1_image_NWKZ-38MM-KIT-006.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\001_image_53400067.jpg</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>911</v>
+        <v>520</v>
       </c>
       <c r="F14" t="n">
-        <v>564</v>
+        <v>718</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V1125FX01-BLACK</t>
+          <t>54650001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -825,16 +825,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1125FX01-BLACK/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/54650001/001.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\V1125FX01-BLACK\1_image_V1125FX01-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\001_image_54650001.jpg</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>757</v>
+        <v>860</v>
       </c>
       <c r="F15" t="n">
         <v>515</v>
@@ -843,7 +843,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V1N-GEN4R-125X2</t>
+          <t>80460406</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -853,25 +853,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/80460406/001.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\V1N-GEN4R-125X2\1_image_V1N-GEN4R-125X2.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\001_image_80460406.jpg</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>778</v>
+        <v>520</v>
       </c>
       <c r="F16" t="n">
-        <v>515</v>
+        <v>718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V1N-GEN4R-125X3</t>
+          <t>80460419</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -881,473 +881,473 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/80460419/001.jpg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\V1N-GEN4R-125X3\1_image_V1N-GEN4R-125X3.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\001_image_80460419.jpg</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>790</v>
+        <v>520</v>
       </c>
       <c r="F17" t="n">
-        <v>515</v>
+        <v>718</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>125V1FX92-BLACK</t>
+          <t>BN-PM-12-light-beige</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/125V1FX92-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/001.jpg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\125V1FX92-BLACK\2_image_125V1FX92-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-light-beige\001_image_BN-PM-12-light-beige.jpg</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>515</v>
+        <v>578</v>
       </c>
       <c r="F18" t="n">
-        <v>841</v>
+        <v>800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>125V1GENAV37-BLACK</t>
+          <t>BN-PM-12-navy-blue</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/125V1GENAV37-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/001.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\125V1GENAV37-BLACK\2_image_125V1GENAV37-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-navy-blue\001_image_BN-PM-12-navy-blue.jpg</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="F19" t="n">
-        <v>769</v>
+        <v>800</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>150V1GENAV36-BLACK</t>
+          <t>BN-PM-12-red</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/150V1GENAV36-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-red/001.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\150V1GENAV36-BLACK\2_image_150V1GENAV36-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-red\001_image_BN-PM-12-red.jpg</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>515</v>
+        <v>578</v>
       </c>
       <c r="F20" t="n">
-        <v>830</v>
+        <v>800</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>150VFX85-BLACK</t>
+          <t>DRS17009-1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/150VFX85-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/001.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\150VFX85-BLACK\2_image_150VFX85-BLACK.jpg.png</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17009-1\001_image_DRS17009-1.jpg</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="F21" t="n">
-        <v>799</v>
+        <v>685</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>DRS17012-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18010/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/001.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\18010\2_image_18010.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17012-1\001_image_DRS17012-1.jpg</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1930</v>
+        <v>759</v>
       </c>
       <c r="F22" t="n">
-        <v>519</v>
+        <v>737</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>DRS17015-1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18240/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/001.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\18240\2_image_18240.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17015-1\001_image_DRS17015-1.jpg</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2383</v>
+        <v>706</v>
       </c>
       <c r="F23" t="n">
-        <v>515</v>
+        <v>732</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BN-BELT-3-FLINT</t>
+          <t>DRS17038-1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-3-FLINT/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/001.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-3-FLINT\2_image_BN-BELT-3-FLINT.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17038-1\001_image_DRS17038-1.jpg</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>608</v>
+        <v>772</v>
       </c>
       <c r="F24" t="n">
-        <v>525</v>
+        <v>700</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BN-BELT-3-RAVEN</t>
+          <t>DRS17082-1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-3-RAVEN/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/001.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-3-RAVEN\2_image_BN-BELT-3-RAVEN.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17082-1\001_image_DRS17082-1.jpg</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>799</v>
+        <v>1073</v>
       </c>
       <c r="F25" t="n">
-        <v>799</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BN-BELT-8-RAVEN</t>
+          <t>DRS17083-1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-8-RAVEN/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/001.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-8-RAVEN\2_image_BN-BELT-8-RAVEN.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17083-1\001_image_DRS17083-1.jpg</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>515</v>
+        <v>785</v>
       </c>
       <c r="F26" t="n">
-        <v>536</v>
+        <v>763</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BS70106-01</t>
+          <t>DRS17203-1-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BS70106-01/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/001.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BS70106-01\2_image_BS70106-01.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17203-1-26\001_image_DRS17203-1-26.jpg</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>899</v>
+        <v>1102</v>
       </c>
       <c r="F27" t="n">
-        <v>899</v>
+        <v>515</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NEW-ALN-010</t>
+          <t>DRS17306-1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NEW-ALN-010/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/001.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NEW-ALN-010\2_image_NEW-ALN-010.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17306-1\001_image_DRS17306-1.jpg</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="F28" t="n">
-        <v>668</v>
+        <v>899</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NW-TUR-35K-0014</t>
+          <t>DRS17708-1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NW-TUR-35K-0014/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/001.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NW-TUR-35K-0014\2_image_NW-TUR-35K-0014.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17708-1\001_image_DRS17708-1.jpg</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="F29" t="n">
-        <v>624</v>
+        <v>899</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NW-TUR-35K-0016</t>
+          <t>DRS17927-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NW-TUR-35K-0016/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/001.jpg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NW-TUR-35K-0016\2_image_NW-TUR-35K-0016.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17927-1\001_image_DRS17927-1.jpg</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="F30" t="n">
-        <v>660</v>
+        <v>899</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NWKZ-38MM-KIT-006</t>
+          <t>L340-037744</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NWKZ-38MM-KIT-006/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/001.jpg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NWKZ-38MM-KIT-006\2_image_NWKZ-38MM-KIT-006.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\001_image_L340-037744.jpg</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>859</v>
+        <v>999</v>
       </c>
       <c r="F31" t="n">
-        <v>820</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V1125FX01-BLACK</t>
+          <t>ua-33mkr-0014-1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1125FX01-BLACK/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/ua-33mkr-0014-1/001.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\V1125FX01-BLACK\2_image_V1125FX01-BLACK.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\ua-33mkr-0014-1\001_image_ua-33mkr-0014-1.jpg</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>515</v>
+        <v>850</v>
       </c>
       <c r="F32" t="n">
-        <v>993</v>
+        <v>755</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V1N-GEN4R-125X2</t>
+          <t>WELL-11705</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>001.jpg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X2/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11705/001.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\V1N-GEN4R-125X2\2_image_V1N-GEN4R-125X2.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\WELL-11705\001_image_WELL-11705.jpg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>799</v>
+        <v>1200</v>
       </c>
       <c r="F33" t="n">
-        <v>799</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V1N-GEN4R-125X3</t>
+          <t>1065618885</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1357,128 +1357,128 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X3/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/1065618885/002.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\V1N-GEN4R-125X3\2_image_V1N-GEN4R-125X3.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\1065618885\2_image_1065618885.jpg</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>799</v>
+        <v>963</v>
       </c>
       <c r="F34" t="n">
-        <v>799</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>30311066</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18010/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311066/002.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\18010\3_image_18010.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\30311066\2_image_30311066.jpg</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1122</v>
+        <v>689</v>
       </c>
       <c r="F35" t="n">
-        <v>1021</v>
+        <v>515</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>30311067</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/18240/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311067/002.jpg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\18240\3_image_18240.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\30311067\2_image_30311067.jpg</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1114</v>
+        <v>670</v>
       </c>
       <c r="F36" t="n">
-        <v>1097</v>
+        <v>515</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BN-BELT-3-FLINT</t>
+          <t>30311068</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-3-FLINT/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/30311068/002.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-3-FLINT\3_image_BN-BELT-3-FLINT.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\30311068\2_image_30311068.jpg</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>567</v>
+        <v>677</v>
       </c>
       <c r="F37" t="n">
-        <v>532</v>
+        <v>515</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BN-BELT-8-RAVEN</t>
+          <t>31211120</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-8-RAVEN/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/31211120/002.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-8-RAVEN\3_image_BN-BELT-8-RAVEN.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\31211120\2_image_31211120.jpg</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>679</v>
+        <v>902</v>
       </c>
       <c r="F38" t="n">
         <v>515</v>
@@ -1487,337 +1487,4957 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BS70106-01</t>
+          <t>50223060</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BS70106-01/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223060/002.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BS70106-01\3_image_BS70106-01.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223060\2_image_50223060.jpg</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>899</v>
+        <v>520</v>
       </c>
       <c r="F39" t="n">
-        <v>899</v>
+        <v>718</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NEW-ALN-010</t>
+          <t>50223161</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NEW-ALN-010/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223161/002.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NEW-ALN-010\3_image_NEW-ALN-010.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223161\2_image_50223161.jpg</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>893</v>
+        <v>520</v>
       </c>
       <c r="F40" t="n">
-        <v>820</v>
+        <v>718</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NWKZ-38MM-KIT-006</t>
+          <t>50223401</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NWKZ-38MM-KIT-006/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/50223401/002.jpg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NWKZ-38MM-KIT-006\3_image_NWKZ-38MM-KIT-006.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223401\2_image_50223401.jpg</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>885</v>
+        <v>520</v>
       </c>
       <c r="F41" t="n">
-        <v>563</v>
+        <v>718</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V1N-GEN4R-125X2</t>
+          <t>51411101</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X2/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411101/002.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\V1N-GEN4R-125X2\3_image_V1N-GEN4R-125X2.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\2_image_51411101.jpg</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>799</v>
+        <v>520</v>
       </c>
       <c r="F42" t="n">
-        <v>799</v>
+        <v>718</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V1N-GEN4R-125X3</t>
+          <t>53400066</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/V1N-GEN4R-125X3/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400066/002.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\V1N-GEN4R-125X3\3_image_V1N-GEN4R-125X3.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400066\2_image_53400066.jpg</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>799</v>
+        <v>520</v>
       </c>
       <c r="F43" t="n">
-        <v>799</v>
+        <v>718</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BN-BELT-3-RAVEN</t>
+          <t>53400067</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-3-RAVEN/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/53400067/002.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-3-RAVEN\4_image_BN-BELT-3-RAVEN.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\2_image_53400067.jpg</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>799</v>
+        <v>520</v>
       </c>
       <c r="F44" t="n">
-        <v>799</v>
+        <v>718</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BS70106-01</t>
+          <t>54650001</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BS70106-01/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/54650001/002.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BS70106-01\4_image_BS70106-01.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\2_image_54650001.jpg</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>881</v>
+        <v>520</v>
       </c>
       <c r="F45" t="n">
-        <v>519</v>
+        <v>718</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NEW-ALN-010</t>
+          <t>80460406</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NEW-ALN-010/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/80460406/002.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NEW-ALN-010\4_image_NEW-ALN-010.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\2_image_80460406.jpg</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>792</v>
+        <v>520</v>
       </c>
       <c r="F46" t="n">
-        <v>899</v>
+        <v>718</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BN-BELT-3-FLINT</t>
+          <t>80460419</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BN-BELT-3-FLINT/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/80460419/002.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BN-BELT-3-FLINT\5_image_BN-BELT-3-FLINT.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\2_image_80460419.jpg</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>609</v>
+        <v>520</v>
       </c>
       <c r="F47" t="n">
-        <v>589</v>
+        <v>718</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BS70106-01</t>
+          <t>BN-PM-12-light-beige</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/BS70106-01/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/002.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BS70106-01\5_image_BS70106-01.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-light-beige\2_image_BN-PM-12-light-beige.jpg</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>634</v>
+        <v>578</v>
       </c>
       <c r="F48" t="n">
-        <v>725</v>
+        <v>800</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NEW-ALN-010</t>
+          <t>BN-PM-12-navy-blue</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/NEW-ALN-010/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/002.jpg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\NEW-ALN-010\5_image_NEW-ALN-010.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-navy-blue\2_image_BN-PM-12-navy-blue.jpg</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>801</v>
+        <v>578</v>
       </c>
       <c r="F49" t="n">
-        <v>833</v>
+        <v>800</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BS70106-01</t>
+          <t>BN-PM-12-red</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>002.jpg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-red/002.jpg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-red\2_image_BN-PM-12-red.jpg</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>578</v>
+      </c>
+      <c r="F50" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DRS17009-1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>002.jpg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/002.jpg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17009-1\2_image_DRS17009-1.jpg</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>899</v>
+      </c>
+      <c r="F51" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DRS17012-1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>002.jpg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/002.jpg</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17012-1\2_image_DRS17012-1.jpg</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>723</v>
+      </c>
+      <c r="F52" t="n">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DRS17015-1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>002.jpg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/002.jpg</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17015-1\2_image_DRS17015-1.jpg</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>899</v>
+      </c>
+      <c r="F53" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DRS17038-1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>002.jpg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/002.jpg</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17038-1\2_image_DRS17038-1.jpg</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>899</v>
+      </c>
+      <c r="F54" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DRS17082-1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>002.jpg</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/002.jpg</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17082-1\2_image_DRS17082-1.jpg</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>899</v>
+      </c>
+      <c r="F55" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DRS17083-1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>002.jpg</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/002.jpg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17083-1\2_image_DRS17083-1.jpg</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>738</v>
+      </c>
+      <c r="F56" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DRS17203-1-26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>002.jpg</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/002.jpg</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17203-1-26\2_image_DRS17203-1-26.jpg</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>899</v>
+      </c>
+      <c r="F57" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1065618885</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/1065618885/003.jpg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\1065618885\3_image_1065618885.jpg</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>949</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>31111120</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/31111120/003.jpg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\31111120\3_image_31111120.jpg</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1293</v>
+      </c>
+      <c r="F59" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>31211120</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/31211120/003.jpg</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\31211120\3_image_31211120.jpg</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>515</v>
+      </c>
+      <c r="F60" t="n">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>50223060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223060/003.jpg</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223060\3_image_50223060.jpg</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>520</v>
+      </c>
+      <c r="F61" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>50223161</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223161/003.jpg</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223161\3_image_50223161.jpg</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>520</v>
+      </c>
+      <c r="F62" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>50223401</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223401/003.jpg</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223401\3_image_50223401.jpg</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>520</v>
+      </c>
+      <c r="F63" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>50223406</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223406/003.jpg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223406\3_image_50223406.jpg</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>520</v>
+      </c>
+      <c r="F64" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>51411101</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411101/003.jpg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\3_image_51411101.jpg</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>520</v>
+      </c>
+      <c r="F65" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>53400067</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400067/003.jpg</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\3_image_53400067.jpg</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>520</v>
+      </c>
+      <c r="F66" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/003.jpg</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\3_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>520</v>
+      </c>
+      <c r="F67" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/003.jpg</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\3_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>520</v>
+      </c>
+      <c r="F68" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/003.jpg</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\3_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>520</v>
+      </c>
+      <c r="F69" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BN-PM-12-navy-blue</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-navy-blue/003.jpg</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-navy-blue\3_image_BN-PM-12-navy-blue.jpg</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>578</v>
+      </c>
+      <c r="F70" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BN-PM-12-red</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-red/003.jpg</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-red\3_image_BN-PM-12-red.jpg</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>578</v>
+      </c>
+      <c r="F71" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DRS17012-1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/003.jpg</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17012-1\3_image_DRS17012-1.jpg</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>823</v>
+      </c>
+      <c r="F72" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DRS17083-1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/003.jpg</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17083-1\3_image_DRS17083-1.jpg</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>698</v>
+      </c>
+      <c r="F73" t="n">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DRS17203-1-26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/003.jpg</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17203-1-26\3_image_DRS17203-1-26.jpg</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>899</v>
+      </c>
+      <c r="F74" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DRS17306-1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/003.jpg</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17306-1\3_image_DRS17306-1.jpg</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>829</v>
+      </c>
+      <c r="F75" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DRS17708-1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/003.jpg</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17708-1\3_image_DRS17708-1.jpg</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>516</v>
+      </c>
+      <c r="F76" t="n">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DRS17927-1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/003.jpg</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17927-1\3_image_DRS17927-1.jpg</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>899</v>
+      </c>
+      <c r="F77" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/003.jpg</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\3_image_L340-037744.jpg</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>999</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WELL-11705</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>003.jpg</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11705/003.jpg</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\WELL-11705\3_image_WELL-11705.jpg</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1065618885</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/1065618885/004.jpg</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\1065618885\4_image_1065618885.jpg</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1114</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>31111120</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/31111120/004.jpg</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\31111120\4_image_31111120.jpg</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>628</v>
+      </c>
+      <c r="F81" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>50223060</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223060/004.jpg</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223060\4_image_50223060.jpg</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>520</v>
+      </c>
+      <c r="F82" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>50223401</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223401/004.jpg</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223401\4_image_50223401.jpg</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>520</v>
+      </c>
+      <c r="F83" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>50223406</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223406/004.jpg</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223406\4_image_50223406.jpg</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>520</v>
+      </c>
+      <c r="F84" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>51411101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411101/004.jpg</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\4_image_51411101.jpg</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>520</v>
+      </c>
+      <c r="F85" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>53400066</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400066/004.jpg</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400066\4_image_53400066.jpg</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>520</v>
+      </c>
+      <c r="F86" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>53400067</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400067/004.jpg</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\4_image_53400067.jpg</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>520</v>
+      </c>
+      <c r="F87" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/004.jpg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\4_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>520</v>
+      </c>
+      <c r="F88" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/004.jpg</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\4_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>520</v>
+      </c>
+      <c r="F89" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/004.jpg</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\4_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>520</v>
+      </c>
+      <c r="F90" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BN-PM-12-light-beige</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-light-beige/004.jpg</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-light-beige\004_image_BN-PM-12-light-beige.jpg</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>578</v>
+      </c>
+      <c r="F91" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BN-PM-12-red</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/BN-PM-12-red/004.jpg</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\BN-PM-12-red\4_image_BN-PM-12-red.jpg</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>578</v>
+      </c>
+      <c r="F92" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DRS17009-1</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17009-1\4_image_DRS17009-1.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>794</v>
+      </c>
+      <c r="F93" t="n">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DRS17012-1</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17012-1\4_image_DRS17012-1.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>942</v>
+      </c>
+      <c r="F94" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DRS17015-1</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17015-1\4_image_DRS17015-1.jpg</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>760</v>
+      </c>
+      <c r="F95" t="n">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DRS17038-1</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17038-1\4_image_DRS17038-1.jpg</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>808</v>
+      </c>
+      <c r="F96" t="n">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DRS17082-1</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17082-1\4_image_DRS17082-1.jpg</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1023</v>
+      </c>
+      <c r="F97" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DRS17083-1</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17083-1\4_image_DRS17083-1.jpg</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>899</v>
+      </c>
+      <c r="F98" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DRS17306-1</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17306-1\4_image_DRS17306-1.jpg</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>947</v>
+      </c>
+      <c r="F99" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DRS17708-1</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17708-1\4_image_DRS17708-1.jpg</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>773</v>
+      </c>
+      <c r="F100" t="n">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DRS17927-1</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/004.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17927-1\4_image_DRS17927-1.jpg</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>934</v>
+      </c>
+      <c r="F101" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/004.jpg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\4_image_L340-037744.jpg</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>999</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>WELL-11705</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>004.jpg</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11705/004.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\WELL-11705\4_image_WELL-11705.jpg</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>31111120</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/31111120/005.jpg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\31111120\5_image_31111120.jpg</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1291</v>
+      </c>
+      <c r="F104" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>50223060</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223060/005.jpg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223060\5_image_50223060.jpg</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>520</v>
+      </c>
+      <c r="F105" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>50223161</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223161/005.jpg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223161\5_image_50223161.jpg</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>520</v>
+      </c>
+      <c r="F106" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>50223401</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223401/005.jpg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223401\5_image_50223401.jpg</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>520</v>
+      </c>
+      <c r="F107" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>50223406</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223406/005.jpg</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223406\5_image_50223406.jpg</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>520</v>
+      </c>
+      <c r="F108" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>53400066</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400066/005.jpg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400066\5_image_53400066.jpg</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>520</v>
+      </c>
+      <c r="F109" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>53400067</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400067/005.jpg</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\5_image_53400067.jpg</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>520</v>
+      </c>
+      <c r="F110" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/005.jpg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\5_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>520</v>
+      </c>
+      <c r="F111" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/005.jpg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\5_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>520</v>
+      </c>
+      <c r="F112" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/005.jpg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\5_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>520</v>
+      </c>
+      <c r="F113" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DRS17009-1</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17009-1\5_image_DRS17009-1.jpg</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>899</v>
+      </c>
+      <c r="F114" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DRS17012-1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17012-1\5_image_DRS17012-1.jpg</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>899</v>
+      </c>
+      <c r="F115" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DRS17015-1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17015-1\5_image_DRS17015-1.jpg</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>899</v>
+      </c>
+      <c r="F116" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DRS17038-1</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17038-1\5_image_DRS17038-1.jpg</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>899</v>
+      </c>
+      <c r="F117" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DRS17082-1</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17082-1\5_image_DRS17082-1.jpg</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>899</v>
+      </c>
+      <c r="F118" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DRS17083-1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17083-1\5_image_DRS17083-1.jpg</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>899</v>
+      </c>
+      <c r="F119" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DRS17203-1-26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/005.jpg</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17203-1-26\5_image_DRS17203-1-26.jpg</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F120" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DRS17306-1</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17306-1\5_image_DRS17306-1.jpg</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>899</v>
+      </c>
+      <c r="F121" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>DRS17708-1</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17708-1\5_image_DRS17708-1.jpg</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>749</v>
+      </c>
+      <c r="F122" t="n">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DRS17927-1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/005.jpg</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17927-1\5_image_DRS17927-1.jpg</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>855</v>
+      </c>
+      <c r="F123" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/005.jpg</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\5_image_L340-037744.jpg</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>959</v>
+      </c>
+      <c r="F124" t="n">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>WELL-11705</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>005.jpg</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/WELL-11705/005.jpg</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\WELL-11705\005_image_WELL-11705.jpg</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1065618885</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>006.jpg</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/BS70106-01/006.jpg</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/обрвзані фоо\BS70106-01\6_image_BS70106-01.jpg</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>890</v>
-      </c>
-      <c r="F50" t="n">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/1065618885/006.jpg</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\1065618885\6_image_1065618885.jpg</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>31111120</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/31111120/006.jpg</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\31111120\006_image_31111120.jpg</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>539</v>
+      </c>
+      <c r="F127" t="n">
         <v>515</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>50223161</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223161/006.jpg</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223161\6_image_50223161.jpg</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>520</v>
+      </c>
+      <c r="F128" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>50223406</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223406/006.jpg</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223406\6_image_50223406.jpg</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>520</v>
+      </c>
+      <c r="F129" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>51411101</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411101/006.jpg</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\6_image_51411101.jpg</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>520</v>
+      </c>
+      <c r="F130" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>53400066</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400066/006.jpg</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400066\6_image_53400066.jpg</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>520</v>
+      </c>
+      <c r="F131" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/006.jpg</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\6_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>520</v>
+      </c>
+      <c r="F132" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/006.jpg</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\6_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>520</v>
+      </c>
+      <c r="F133" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/006.jpg</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\6_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>520</v>
+      </c>
+      <c r="F134" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DRS17009-1</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17009-1\6_image_DRS17009-1.jpg</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>899</v>
+      </c>
+      <c r="F135" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>DRS17012-1</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17012-1\6_image_DRS17012-1.jpg</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>899</v>
+      </c>
+      <c r="F136" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>DRS17015-1</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17015-1\6_image_DRS17015-1.jpg</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>911</v>
+      </c>
+      <c r="F137" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>DRS17038-1</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17038-1\6_image_DRS17038-1.jpg</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>899</v>
+      </c>
+      <c r="F138" t="n">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>DRS17082-1</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17082-1\6_image_DRS17082-1.jpg</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>1059</v>
+      </c>
+      <c r="F139" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>DRS17083-1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17083-1\6_image_DRS17083-1.jpg</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>899</v>
+      </c>
+      <c r="F140" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>DRS17203-1-26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/006.jpg</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17203-1-26\6_image_DRS17203-1-26.jpg</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>899</v>
+      </c>
+      <c r="F141" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>DRS17306-1</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17306-1\6_image_DRS17306-1.jpg</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1063</v>
+      </c>
+      <c r="F142" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DRS17708-1</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17708-1\6_image_DRS17708-1.jpg</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>879</v>
+      </c>
+      <c r="F143" t="n">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>DRS17927-1</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/006.jpg</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17927-1\6_image_DRS17927-1.jpg</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>899</v>
+      </c>
+      <c r="F144" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>006.jpg</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/006.jpg</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\6_image_L340-037744.jpg</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>926</v>
+      </c>
+      <c r="F145" t="n">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1065618885</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/1065618885/007.jpg</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\1065618885\007_image_1065618885.jpg</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>1203</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>50223060</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223060/007.jpg</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223060\7_image_50223060.jpg</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>520</v>
+      </c>
+      <c r="F147" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>50223161</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223161/007.jpg</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223161\7_image_50223161.jpg</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>520</v>
+      </c>
+      <c r="F148" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>50223401</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223401/007.jpg</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223401\7_image_50223401.jpg</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>520</v>
+      </c>
+      <c r="F149" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>50223406</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223406/007.jpg</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223406\7_image_50223406.jpg</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>520</v>
+      </c>
+      <c r="F150" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>51411101</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411101/007.jpg</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\7_image_51411101.jpg</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>520</v>
+      </c>
+      <c r="F151" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>53400066</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400066/007.jpg</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400066\7_image_53400066.jpg</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>520</v>
+      </c>
+      <c r="F152" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>53400067</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400067/007.jpg</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\7_image_53400067.jpg</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>520</v>
+      </c>
+      <c r="F153" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/007.jpg</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\7_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>520</v>
+      </c>
+      <c r="F154" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/007.jpg</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\7_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>520</v>
+      </c>
+      <c r="F155" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/007.jpg</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\7_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>520</v>
+      </c>
+      <c r="F156" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>DRS17009-1</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17009-1\7_image_DRS17009-1.jpg</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>899</v>
+      </c>
+      <c r="F157" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>DRS17012-1</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17012-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17012-1\7_image_DRS17012-1.jpg</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>899</v>
+      </c>
+      <c r="F158" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>DRS17015-1</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17015-1\7_image_DRS17015-1.jpg</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>899</v>
+      </c>
+      <c r="F159" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>DRS17038-1</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17038-1\7_image_DRS17038-1.jpg</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>899</v>
+      </c>
+      <c r="F160" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>DRS17082-1</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17082-1\7_image_DRS17082-1.jpg</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>899</v>
+      </c>
+      <c r="F161" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>DRS17083-1</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17083-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17083-1\7_image_DRS17083-1.jpg</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>899</v>
+      </c>
+      <c r="F162" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DRS17203-1-26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/007.jpg</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17203-1-26\7_image_DRS17203-1-26.jpg</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>899</v>
+      </c>
+      <c r="F163" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DRS17306-1</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17306-1\7_image_DRS17306-1.jpg</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>899</v>
+      </c>
+      <c r="F164" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>DRS17708-1</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17708-1\7_image_DRS17708-1.jpg</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>899</v>
+      </c>
+      <c r="F165" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DRS17927-1</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/007.jpg</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17927-1\7_image_DRS17927-1.jpg</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>899</v>
+      </c>
+      <c r="F166" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>007.jpg</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/007.jpg</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\7_image_L340-037744.jpg</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>872</v>
+      </c>
+      <c r="F167" t="n">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>50223060</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223060/008.jpg</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223060\8_image_50223060.jpg</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>520</v>
+      </c>
+      <c r="F168" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>50223161</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223161/008.jpg</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223161\008_image_50223161.jpg</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>520</v>
+      </c>
+      <c r="F169" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>50223401</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223401/008.jpg</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223401\8_image_50223401.jpg</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>520</v>
+      </c>
+      <c r="F170" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>50223406</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223406/008.jpg</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223406\008_image_50223406.jpg</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>520</v>
+      </c>
+      <c r="F171" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>51411101</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411101/008.jpg</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\8_image_51411101.jpg</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>520</v>
+      </c>
+      <c r="F172" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>53400066</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400066/008.jpg</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400066\8_image_53400066.jpg</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>520</v>
+      </c>
+      <c r="F173" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>53400067</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400067/008.jpg</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\8_image_53400067.jpg</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>520</v>
+      </c>
+      <c r="F174" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/008.jpg</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\8_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>520</v>
+      </c>
+      <c r="F175" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/008.jpg</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\8_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>520</v>
+      </c>
+      <c r="F176" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/008.jpg</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\8_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>520</v>
+      </c>
+      <c r="F177" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>DRS17009-1</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17009-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17009-1\008_image_DRS17009-1.jpg</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>750</v>
+      </c>
+      <c r="F178" t="n">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DRS17015-1</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17015-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17015-1\008_image_DRS17015-1.jpg</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>695</v>
+      </c>
+      <c r="F179" t="n">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>DRS17038-1</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17038-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17038-1\008_image_DRS17038-1.jpg</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>738</v>
+      </c>
+      <c r="F180" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>DRS17082-1</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17082-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17082-1\008_image_DRS17082-1.jpg</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>864</v>
+      </c>
+      <c r="F181" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DRS17203-1-26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/008.jpg</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17203-1-26\8_image_DRS17203-1-26.jpg</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>899</v>
+      </c>
+      <c r="F182" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DRS17306-1</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17306-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17306-1\008_image_DRS17306-1.jpg</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>832</v>
+      </c>
+      <c r="F183" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>DRS17708-1</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17708-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17708-1\008_image_DRS17708-1.jpg</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>585</v>
+      </c>
+      <c r="F184" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DRS17927-1</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/008.jpg</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17927-1\8_image_DRS17927-1.jpg</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>899</v>
+      </c>
+      <c r="F185" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>008.jpg</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/008.jpg</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\8_image_L340-037744.jpg</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>999</v>
+      </c>
+      <c r="F186" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>50223060</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223060/009.jpg</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223060\009_image_50223060.jpg</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>520</v>
+      </c>
+      <c r="F187" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>50223401</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/50223401/009.jpg</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\50223401\009_image_50223401.jpg</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>520</v>
+      </c>
+      <c r="F188" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>51411101</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411101/009.jpg</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\9_image_51411101.jpg</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>520</v>
+      </c>
+      <c r="F189" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>53400066</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400066/009.jpg</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400066\009_image_53400066.jpg</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>520</v>
+      </c>
+      <c r="F190" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>53400067</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400067/009.jpg</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\9_image_53400067.jpg</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>520</v>
+      </c>
+      <c r="F191" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/009.jpg</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\9_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>520</v>
+      </c>
+      <c r="F192" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>DRS17203-1-26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17203-1-26/009.jpg</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17203-1-26\009_image_DRS17203-1-26.jpg</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>925</v>
+      </c>
+      <c r="F193" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>DRS17927-1</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/DRS17927-1/009.jpg</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\DRS17927-1\009_image_DRS17927-1.jpg</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>888</v>
+      </c>
+      <c r="F194" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/009.jpg</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\9_image_L340-037744.jpg</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>999</v>
+      </c>
+      <c r="F195" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>51411101</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411101/010.jpg</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\10_image_51411101.jpg</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>520</v>
+      </c>
+      <c r="F196" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>53400067</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400067/010.jpg</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\10_image_53400067.jpg</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>520</v>
+      </c>
+      <c r="F197" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/010.jpg</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\10_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>743</v>
+      </c>
+      <c r="F198" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/010.jpg</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\10_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>520</v>
+      </c>
+      <c r="F199" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/010.jpg</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\10_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>520</v>
+      </c>
+      <c r="F200" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>L340-037744</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/L340-037744/010.jpg</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\L340-037744\010_image_L340-037744.jpg</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>611</v>
+      </c>
+      <c r="F201" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>51411101</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>011.jpg</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411101/011.jpg</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\51411101\011_image_51411101.jpg</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>520</v>
+      </c>
+      <c r="F202" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>53400067</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>011.jpg</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/53400067/011.jpg</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\53400067\011_image_53400067.jpg</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>520</v>
+      </c>
+      <c r="F203" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>011.jpg</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/011.jpg</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\11_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>911</v>
+      </c>
+      <c r="F204" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>011.jpg</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/011.jpg</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\11_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>520</v>
+      </c>
+      <c r="F205" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>011.jpg</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/011.jpg</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\11_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>520</v>
+      </c>
+      <c r="F206" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>012.jpg</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/012.jpg</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\12_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>651</v>
+      </c>
+      <c r="F207" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>012.jpg</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/012.jpg</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\12_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>520</v>
+      </c>
+      <c r="F208" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>012.jpg</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/012.jpg</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\12_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>520</v>
+      </c>
+      <c r="F209" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>013.jpg</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/013.jpg</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\13_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>1081</v>
+      </c>
+      <c r="F210" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>013.jpg</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/013.jpg</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\13_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>520</v>
+      </c>
+      <c r="F211" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>014.jpg</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/014.jpg</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\14_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>917</v>
+      </c>
+      <c r="F212" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>80460406</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>014.jpg</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460406/014.jpg</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460406\014_image_80460406.jpg</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>520</v>
+      </c>
+      <c r="F213" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>80460419</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>014.jpg</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/80460419/014.jpg</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\80460419\014_image_80460419.jpg</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>520</v>
+      </c>
+      <c r="F214" t="n">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>54650001</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>015.jpg</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/54650001/015.jpg</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/349/фото 349/відзеркалені фото\54650001\015_image_54650001.jpg</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>520</v>
+      </c>
+      <c r="F215" t="n">
+        <v>718</v>
       </c>
     </row>
   </sheetData>

--- a/photo_links.xlsx
+++ b/photo_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WELL-11108</t>
+          <t>WELL-12402</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11108/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12402/001.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-11108\001_image_WELL-11108.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-12402\1_image_WELL-12402.jpg</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1199</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="n">
         <v>1499</v>
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WELL-11901</t>
+          <t>WELL-12508</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -489,25 +489,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11901/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12508/001.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-11901\001_image_WELL-11901.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-12508\001_image_WELL-12508.jpg</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1199</v>
+        <v>988</v>
       </c>
       <c r="F3" t="n">
-        <v>1499</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WELL-13002</t>
+          <t>WELL-46514</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,25 +517,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-13002/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46514/001.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-13002\001_image_WELL-13002.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-46514\001_image_WELL-46514.jpg</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1199</v>
+        <v>942</v>
       </c>
       <c r="F4" t="n">
-        <v>1499</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WELL-13009</t>
+          <t>WELL-47304</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -545,25 +545,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-13009/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47304/001.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-13009\001_image_WELL-13009.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-47304\001_image_WELL-47304.jpg</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="F5" t="n">
-        <v>1499</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WELL-44455</t>
+          <t>WELL-60206</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -573,25 +573,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-44455/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60206/001.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-44455\1_image_WELL-44455.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-60206\1_image_WELL-60206.jpg</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="F6" t="n">
-        <v>1107</v>
+        <v>657</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WELL-45107</t>
+          <t>WELL-61404</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,25 +601,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-45107/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61404/001.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-45107\1_image_WELL-45107.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61404\1_image_WELL-61404.jpg</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1078</v>
+        <v>1199</v>
       </c>
       <c r="F7" t="n">
-        <v>1240</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WELL-46401</t>
+          <t>WELL-61409</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -629,25 +629,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-46401/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61409/001.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-46401\1_image_WELL-46401.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61409\1_image_WELL-61409.jpg</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>847</v>
+        <v>1199</v>
       </c>
       <c r="F8" t="n">
-        <v>1247</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WELL-47309</t>
+          <t>WELL-61600</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,25 +657,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-47309/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61600/001.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-47309\001_image_WELL-47309.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61600\1_image_WELL-61600.jpg</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1199</v>
+        <v>1082</v>
       </c>
       <c r="F9" t="n">
-        <v>1499</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WELL-56311</t>
+          <t>WELL-66802</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -685,25 +685,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-56311/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-66802/001.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-56311\1_image_WELL-56311.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-66802\1_image_WELL-66802.jpg</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1191</v>
+        <v>1033</v>
       </c>
       <c r="F10" t="n">
-        <v>994</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WELL-56510</t>
+          <t>WELL-67209</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -713,25 +713,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-56510/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-67209/001.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-56510\1_image_WELL-56510.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-67209\1_image_WELL-67209.jpg</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="F11" t="n">
-        <v>799</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WELL-56511</t>
+          <t>WELL-68404</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -741,25 +741,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-56511/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-68404/001.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-56511\1_image_WELL-56511.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-68404\001_image_WELL-68404.jpg</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>838</v>
+        <v>1199</v>
       </c>
       <c r="F12" t="n">
-        <v>750</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WELL-60127</t>
+          <t>WELL-69505</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -769,25 +769,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-60127/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-69505/001.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-60127\1_image_WELL-60127.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-69505\001_image_WELL-69505.jpg</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1103</v>
+        <v>1199</v>
       </c>
       <c r="F13" t="n">
-        <v>928</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WELL-60504</t>
+          <t>WELL-69604</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -797,25 +797,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-60504/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-69604/001.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-60504\1_image_WELL-60504.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-69604\001_image_WELL-69604.jpg</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>1199</v>
       </c>
       <c r="F14" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WELL-61013</t>
+          <t>WELL-90201</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -825,72 +825,72 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-61013/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-90201/001.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-61013\1_image_WELL-61013.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-90201\1_image_WELL-90201.jpg</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1176</v>
+        <v>1511</v>
       </c>
       <c r="F15" t="n">
-        <v>900</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WELL-62404</t>
+          <t>WELL-12402</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-62404/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12402/002.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-62404\001_image_WELL-62404.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-12402\2_image_WELL-12402.jpg</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1089</v>
+        <v>1157</v>
       </c>
       <c r="F16" t="n">
-        <v>751</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WELL-63204</t>
+          <t>WELL-12508</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-63204/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12508/002.jpg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-63204\001_image_WELL-63204.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-12508\2_image_WELL-12508.jpg</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="F17" t="n">
         <v>1499</v>
@@ -899,91 +899,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WELL-65621</t>
+          <t>WELL-46514</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-65621/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46514/002.jpg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-65621\1_image_WELL-65621.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-46514\002_image_WELL-46514.jpg</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1256</v>
+        <v>1118</v>
       </c>
       <c r="F18" t="n">
-        <v>827</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WELL-70101</t>
+          <t>WELL-47304</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-70101/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47304/002.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-70101\1_image_WELL-70101.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-47304\2_image_WELL-47304.jpg</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>530</v>
+        <v>1033</v>
       </c>
       <c r="F19" t="n">
-        <v>710</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WELL-70104</t>
+          <t>WELL-60206</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-70104/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-60206/002.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-70104\1_image_WELL-70104.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-60206\2_image_WELL-60206.jpg</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>530</v>
+        <v>772</v>
       </c>
       <c r="F20" t="n">
-        <v>702</v>
+        <v>800</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WELL-11108</t>
+          <t>WELL-61404</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11108/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61404/002.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-11108\2_image_WELL-11108.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61404\2_image_WELL-61404.jpg</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WELL-11901</t>
+          <t>WELL-61409</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11901/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61409/002.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-11901\2_image_WELL-11901.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61409\2_image_WELL-61409.jpg</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1039,7 +1039,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WELL-44455</t>
+          <t>WELL-61600</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,25 +1049,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-44455/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61600/002.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-44455\2_image_WELL-44455.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61600\2_image_WELL-61600.jpg</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="F23" t="n">
-        <v>1186</v>
+        <v>783</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WELL-45107</t>
+          <t>WELL-66802</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,25 +1077,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-45107/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-66802/002.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-45107\2_image_WELL-45107.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-66802\2_image_WELL-66802.jpg</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1064</v>
+        <v>1033</v>
       </c>
       <c r="F24" t="n">
-        <v>1318</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WELL-46401</t>
+          <t>WELL-67209</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1105,25 +1105,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-46401/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-67209/002.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-46401\2_image_WELL-46401.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-67209\2_image_WELL-67209.jpg</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="F25" t="n">
-        <v>1391</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WELL-56311</t>
+          <t>WELL-90201</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1133,249 +1133,249 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-56311/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-90201/002.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-56311\2_image_WELL-56311.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-90201\2_image_WELL-90201.jpg</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1057</v>
+        <v>1500</v>
       </c>
       <c r="F26" t="n">
-        <v>951</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WELL-56510</t>
+          <t>WELL-12402</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-56510/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12402/003.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-56510\2_image_WELL-56510.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-12402\3_image_WELL-12402.jpg</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1149</v>
+        <v>1199</v>
       </c>
       <c r="F27" t="n">
-        <v>807</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WELL-56511</t>
+          <t>WELL-46514</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-56511/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46514/003.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-56511\2_image_WELL-56511.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-46514\003_image_WELL-46514.jpg</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1122</v>
+        <v>1199</v>
       </c>
       <c r="F28" t="n">
-        <v>843</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WELL-60127</t>
+          <t>WELL-61404</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-60127/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61404/003.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-60127\2_image_WELL-60127.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61404\3_image_WELL-61404.jpg</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1009</v>
+        <v>1199</v>
       </c>
       <c r="F29" t="n">
-        <v>1017</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WELL-60504</t>
+          <t>WELL-61409</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-60504/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61409/003.jpg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-60504\2_image_WELL-60504.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61409\3_image_WELL-61409.jpg</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>1199</v>
       </c>
       <c r="F30" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WELL-61013</t>
+          <t>WELL-61600</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-61013/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61600/003.jpg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-61013\2_image_WELL-61013.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61600\3_image_WELL-61600.jpg</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1176</v>
+        <v>1079</v>
       </c>
       <c r="F31" t="n">
-        <v>892</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WELL-65621</t>
+          <t>WELL-66802</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-65621/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-66802/003.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-65621\2_image_WELL-65621.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-66802\3_image_WELL-66802.jpg</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1537</v>
+        <v>825</v>
       </c>
       <c r="F32" t="n">
-        <v>1578</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WELL-70101</t>
+          <t>WELL-68404</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-70101/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-68404/003.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-70101\2_image_WELL-70101.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-68404\3_image_WELL-68404.jpg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>722</v>
+        <v>1199</v>
       </c>
       <c r="F33" t="n">
-        <v>846</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WELL-70104</t>
+          <t>WELL-69505</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-70104/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-69505/003.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-70104\2_image_WELL-70104.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-69505\3_image_WELL-69505.jpg</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F34" t="n">
-        <v>791</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WELL-11108</t>
+          <t>WELL-69604</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11108/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-69604/003.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-11108\3_image_WELL-11108.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-69604\3_image_WELL-69604.jpg</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1403,7 +1403,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WELL-13002</t>
+          <t>WELL-90201</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1413,44 +1413,44 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-13002/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-90201/003.jpg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-13002\3_image_WELL-13002.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-90201\3_image_WELL-90201.jpg</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1199</v>
+        <v>1540</v>
       </c>
       <c r="F36" t="n">
-        <v>1499</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WELL-13009</t>
+          <t>WELL-12508</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-13009/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12508/004.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-13009\3_image_WELL-13009.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-12508\4_image_WELL-12508.jpg</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1199</v>
+        <v>1158</v>
       </c>
       <c r="F37" t="n">
         <v>1499</v>
@@ -1459,78 +1459,78 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WELL-44455</t>
+          <t>WELL-47304</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-44455/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47304/004.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-44455\3_image_WELL-44455.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-47304\4_image_WELL-47304.jpg</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>870</v>
+        <v>1199</v>
       </c>
       <c r="F38" t="n">
-        <v>1289</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WELL-46401</t>
+          <t>WELL-61404</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-46401/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61404/004.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-46401\3_image_WELL-46401.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61404\4_image_WELL-61404.jpg</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>1199</v>
       </c>
       <c r="F39" t="n">
-        <v>943</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WELL-47309</t>
+          <t>WELL-61409</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-47309/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61409/004.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-47309\3_image_WELL-47309.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61409\4_image_WELL-61409.jpg</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1543,246 +1543,246 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WELL-56311</t>
+          <t>WELL-61600</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-56311/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61600/004.jpg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-56311\3_image_WELL-56311.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61600\4_image_WELL-61600.jpg</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1183</v>
+        <v>1079</v>
       </c>
       <c r="F41" t="n">
-        <v>1262</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WELL-60127</t>
+          <t>WELL-66802</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-60127/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-66802/004.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-60127\3_image_WELL-60127.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-66802\4_image_WELL-66802.jpg</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1041</v>
+        <v>802</v>
       </c>
       <c r="F42" t="n">
-        <v>1206</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WELL-60504</t>
+          <t>WELL-68404</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-60504/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-68404/004.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-60504\3_image_WELL-60504.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-68404\4_image_WELL-68404.jpg</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1112</v>
+        <v>736</v>
       </c>
       <c r="F43" t="n">
-        <v>557</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WELL-62404</t>
+          <t>WELL-69505</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-62404/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-69505/004.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-62404\3_image_WELL-62404.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-69505\4_image_WELL-69505.jpg</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1191</v>
+        <v>698</v>
       </c>
       <c r="F44" t="n">
-        <v>864</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WELL-63204</t>
+          <t>WELL-69604</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-63204/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-69604/004.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-63204\3_image_WELL-63204.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-69604\4_image_WELL-69604.jpg</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1199</v>
+        <v>721</v>
       </c>
       <c r="F45" t="n">
-        <v>1498</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WELL-65621</t>
+          <t>WELL-12508</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-65621/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-12508/005.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-65621\3_image_WELL-65621.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-12508\005_image_WELL-12508.jpg</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>942</v>
+        <v>1199</v>
       </c>
       <c r="F46" t="n">
-        <v>1196</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WELL-70101</t>
+          <t>WELL-46514</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-70101/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46514/005.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-70101\3_image_WELL-70101.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-46514\5_image_WELL-46514.jpg</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>735</v>
+        <v>1140</v>
       </c>
       <c r="F47" t="n">
-        <v>561</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WELL-70104</t>
+          <t>WELL-47304</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-70104/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47304/005.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-70104\3_image_WELL-70104.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-47304\5_image_WELL-47304.jpg</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>749</v>
+        <v>1199</v>
       </c>
       <c r="F48" t="n">
-        <v>571</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WELL-11901</t>
+          <t>WELL-61404</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11901/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61404/005.jpg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-11901\4_image_WELL-11901.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61404\5_image_WELL-61404.jpg</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1795,22 +1795,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WELL-13002</t>
+          <t>WELL-61409</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-13002/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61409/005.jpg</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-13002\4_image_WELL-13002.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61409\5_image_WELL-61409.jpg</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1823,106 +1823,106 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WELL-13009</t>
+          <t>WELL-61600</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-13009/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-61600/005.jpg</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-13009\4_image_WELL-13009.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-61600\5_image_WELL-61600.jpg</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1199</v>
+        <v>794</v>
       </c>
       <c r="F51" t="n">
-        <v>1499</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WELL-46401</t>
+          <t>WELL-66802</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-46401/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-66802/005.jpg</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-46401\4_image_WELL-46401.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-66802\5_image_WELL-66802.jpg</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1130</v>
+        <v>1160</v>
       </c>
       <c r="F52" t="n">
-        <v>1313</v>
+        <v>781</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WELL-47309</t>
+          <t>WELL-68404</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-47309/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-68404/005.jpg</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-47309\4_image_WELL-47309.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-68404\5_image_WELL-68404.jpg</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>992</v>
+        <v>717</v>
       </c>
       <c r="F53" t="n">
-        <v>1401</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WELL-60504</t>
+          <t>WELL-69505</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-60504/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-69505/005.jpg</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-60504\4_image_WELL-60504.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-69505\005_image_WELL-69505.jpg</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1935,134 +1935,134 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WELL-62404</t>
+          <t>WELL-69604</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-62404/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-69604/005.jpg</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-62404\4_image_WELL-62404.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-69604\005_image_WELL-69604.jpg</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1070</v>
+        <v>1199</v>
       </c>
       <c r="F55" t="n">
-        <v>876</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WELL-63204</t>
+          <t>WELL-46514</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-63204/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-46514/006.jpg</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-63204\4_image_WELL-63204.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-46514\006_image_WELL-46514.jpg</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1637</v>
+        <v>795</v>
       </c>
       <c r="F56" t="n">
-        <v>2047</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WELL-65621</t>
+          <t>WELL-47304</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-65621/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47304/006.jpg</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-65621\4_image_WELL-65621.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-47304\6_image_WELL-47304.jpg</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1389</v>
+        <v>997</v>
       </c>
       <c r="F57" t="n">
-        <v>1059</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WELL-11901</t>
+          <t>WELL-66802</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11901/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-66802/006.jpg</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-11901\5_image_WELL-11901.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-66802\6_image_WELL-66802.jpg</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>985</v>
+        <v>1199</v>
       </c>
       <c r="F58" t="n">
-        <v>1339</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WELL-13002</t>
+          <t>WELL-68404</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-13002/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-68404/006.jpg</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-13002\005_image_WELL-13002.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-68404\006_image_WELL-68404.jpg</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2075,253 +2075,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WELL-13009</t>
+          <t>WELL-47304</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>007.jpg</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-13009/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/WELL-47304/007.jpg</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-13009\005_image_WELL-13009.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/2/фото/5 посорттовані\WELL-47304\007_image_WELL-47304.jpg</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1199</v>
+        <v>997</v>
       </c>
       <c r="F60" t="n">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>WELL-47309</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>005.jpg</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-47309/005.jpg</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-47309\5_image_WELL-47309.jpg</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>981</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>WELL-60504</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>005.jpg</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-60504/005.jpg</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-60504\5_image_WELL-60504.jpg</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>1199</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>WELL-62404</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>005.jpg</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-62404/005.jpg</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-62404\5_image_WELL-62404.jpg</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>1152</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>WELL-63204</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>005.jpg</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-63204/005.jpg</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-63204\5_image_WELL-63204.jpg</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>1552</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>WELL-11901</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>006.jpg</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-11901/006.jpg</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-11901\006_image_WELL-11901.jpg</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>1199</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>WELL-47309</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>006.jpg</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-47309/006.jpg</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-47309\006_image_WELL-47309.jpg</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>1121</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>WELL-62404</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>006.jpg</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-62404/006.jpg</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-62404\006_image_WELL-62404.jpg</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>967</v>
-      </c>
-      <c r="F67" t="n">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>WELL-63204</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>006.jpg</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>https://oleks-netizen.github.io/product-images/WELL-63204/006.jpg</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/нові товари ВЕЛЛ/фото/5 посортовані\WELL-63204\006_image_WELL-63204.jpg</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>1199</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1499</v>
+        <v>1294</v>
       </c>
     </row>
   </sheetData>

--- a/photo_links.xlsx
+++ b/photo_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>336201100</t>
+          <t>2222-05-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/336201100/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2222-05-31/001.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\336201100\001_image_336201100.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\2222-05-31\001_image_2222-05-31.jpg</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>946</v>
+        <v>530</v>
       </c>
       <c r="F2" t="n">
-        <v>880</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>410011208</t>
+          <t>51311301s</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -489,25 +489,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011208/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/001.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011208\001_image_410011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\001_image_51311301s.jpg</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>950</v>
+        <v>530</v>
       </c>
       <c r="F3" t="n">
-        <v>923</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>410011508</t>
+          <t>51411010s</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,25 +517,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011508/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/001.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011508\001_image_410011508.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\001_image_51411010s.jpg</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>946</v>
+        <v>530</v>
       </c>
       <c r="F4" t="n">
-        <v>684</v>
+        <v>953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>410413701</t>
+          <t>51411215s</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -545,25 +545,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410413701/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/001.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410413701\001_image_410413701.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\001_image_51411215s.jpg</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>936</v>
+        <v>530</v>
       </c>
       <c r="F5" t="n">
-        <v>920</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>415011208</t>
+          <t>51411264s</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -573,25 +573,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/415011208/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/001.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\415011208\001_image_415011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\001_image_51411264s.jpg</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>957</v>
+        <v>530</v>
       </c>
       <c r="F6" t="n">
-        <v>932</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>457011208</t>
+          <t>BN-BAG-62-caramel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,25 +601,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/457011208/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BAG-62-caramel/001.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\457011208\001_image_457011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\BN-BAG-62-caramel\001_image_BN-BAG-62-caramel.jpg</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>950</v>
+        <v>578</v>
       </c>
       <c r="F7" t="n">
-        <v>699</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>51110700108</t>
+          <t>FA-0324-4lx</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -629,25 +629,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51110700108/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-0324-4lx/001.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\51110700108\001_image_51110700108.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\FA-0324-4lx\001_image_FA-0324-4lx.jpg</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="F8" t="n">
-        <v>841</v>
+        <v>685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>512107001</t>
+          <t>GARETH VT BLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,25 +657,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/512107001/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GARETH VT BLK/001.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\512107001\001_image_512107001.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\GARETH VT BLK\001_image_GARETH VT BLK.jpg</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>903</v>
+        <v>943</v>
       </c>
       <c r="F9" t="n">
-        <v>934</v>
+        <v>835</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tur-1</t>
+          <t>RA-3107-4lx</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -685,25 +685,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-1/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RA-3107-4lx/001.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-1\001_image_tur-1.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RA-3107-4lx\001_image_RA-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>934</v>
+        <v>956</v>
       </c>
       <c r="F10" t="n">
-        <v>798</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tur-2</t>
+          <t>RC-0001-4lx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -713,25 +713,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-2/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/001.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-2\001_image_tur-2.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\001_image_RC-0001-4lx.jpg</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="F11" t="n">
-        <v>860</v>
+        <v>833</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tur-3</t>
+          <t>RC-3107-4lx</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -741,25 +741,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-3/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-3107-4lx/001.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-3\001_image_tur-3.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-3107-4lx\001_image_RC-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>940</v>
+        <v>955</v>
       </c>
       <c r="F12" t="n">
-        <v>855</v>
+        <v>569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-10</t>
+          <t>RC-8839-4lx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -769,25 +769,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-10/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/001.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-10\001_image_ua-avtmt-35k-10.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\001_image_RC-8839-4lx.jpg</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>889</v>
+        <v>904</v>
       </c>
       <c r="F13" t="n">
-        <v>623</v>
+        <v>878</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-11</t>
+          <t>RE-3107-4lx</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -797,25 +797,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-11/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx/001.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-11\001_image_ua-avtmt-35k-11.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx\001_image_RE-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1065</v>
+        <v>952</v>
       </c>
       <c r="F14" t="n">
-        <v>530</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-12</t>
+          <t>RE-3107-4lx-96888</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -825,25 +825,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-12/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx-96888/001.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-12\001_image_ua-avtmt-35k-12.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx-96888\001_image_RE-3107-4lx-96888.jpg</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="F15" t="n">
-        <v>530</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-13</t>
+          <t>RYv-3107-4lx</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -853,277 +853,277 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-13/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RYv-3107-4lx/001.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-13\001_image_ua-avtmt-35k-13.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RYv-3107-4lx\001_image_RYv-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>894</v>
+        <v>969</v>
       </c>
       <c r="F16" t="n">
-        <v>602</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-14</t>
+          <t>2222-05-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-14/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2222-05-31/002.jpg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-14\001_image_ua-avtmt-35k-14.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\2222-05-31\2_image_2222-05-31.jpg</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>919</v>
+        <v>530</v>
       </c>
       <c r="F17" t="n">
-        <v>530</v>
+        <v>924</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-15</t>
+          <t>51311301s</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-15/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/002.jpg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-15\001_image_ua-avtmt-35k-15.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\2_image_51311301s.jpg</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1206</v>
+        <v>530</v>
       </c>
       <c r="F18" t="n">
-        <v>530</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-16</t>
+          <t>51411010s</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-16/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/002.jpg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-16\001_image_ua-avtmt-35k-16.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\2_image_51411010s.jpg</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>907</v>
+        <v>530</v>
       </c>
       <c r="F19" t="n">
-        <v>549</v>
+        <v>893</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-17</t>
+          <t>51411215s</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-17/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/002.jpg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-17\001_image_ua-avtmt-35k-17.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\2_image_51411215s.jpg</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>880</v>
+        <v>530</v>
       </c>
       <c r="F20" t="n">
-        <v>542</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-18</t>
+          <t>51411264s</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-18/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/002.jpg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-18\001_image_ua-avtmt-35k-18.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\2_image_51411264s.jpg</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>530</v>
       </c>
       <c r="F21" t="n">
-        <v>530</v>
+        <v>964</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-19</t>
+          <t>BN-BAG-62-caramel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-19/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BAG-62-caramel/002.jpg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-19\001_image_ua-avtmt-35k-19.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\BN-BAG-62-caramel\2_image_BN-BAG-62-caramel.jpg</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>909</v>
+        <v>582</v>
       </c>
       <c r="F22" t="n">
-        <v>556</v>
+        <v>800</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-20</t>
+          <t>FA-0324-4lx</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-20/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-0324-4lx/002.jpg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-20\001_image_ua-avtmt-35k-20.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\FA-0324-4lx\2_image_FA-0324-4lx.jpg</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>911</v>
+        <v>578</v>
       </c>
       <c r="F23" t="n">
-        <v>536</v>
+        <v>916</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-21</t>
+          <t>GARETH VT BLK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-21/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GARETH VT BLK/002.jpg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-21\001_image_ua-avtmt-35k-21.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\GARETH VT BLK\2_image_GARETH VT BLK.jpg</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>879</v>
+        <v>967</v>
       </c>
       <c r="F24" t="n">
-        <v>533</v>
+        <v>930</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-22</t>
+          <t>RA-3107-4lx</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>001.jpg</t>
+          <t>002.jpg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-22/001.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RA-3107-4lx/002.jpg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-22\001_image_ua-avtmt-35k-22.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RA-3107-4lx\2_image_RA-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>880</v>
+        <v>957</v>
       </c>
       <c r="F25" t="n">
-        <v>595</v>
+        <v>819</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>336201100</t>
+          <t>RC-0001-4lx</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1133,25 +1133,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/336201100/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/002.jpg</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\336201100\002_image_336201100.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\2_image_RC-0001-4lx.jpg</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1729</v>
+        <v>808</v>
       </c>
       <c r="F26" t="n">
-        <v>530</v>
+        <v>794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>410011208</t>
+          <t>RC-3107-4lx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1161,25 +1161,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011208/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-3107-4lx/002.jpg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011208\002_image_410011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-3107-4lx\2_image_RC-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="F27" t="n">
-        <v>884</v>
+        <v>930</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>410011508</t>
+          <t>RC-8839-4lx</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,25 +1189,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011508/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/002.jpg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011508\002_image_410011508.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\2_image_RC-8839-4lx.jpg</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>938</v>
+        <v>970</v>
       </c>
       <c r="F28" t="n">
-        <v>936</v>
+        <v>970</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>410413701</t>
+          <t>RE-3107-4lx</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1217,25 +1217,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410413701/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx/002.jpg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410413701\002_image_410413701.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx\2_image_RE-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>970</v>
+        <v>946</v>
       </c>
       <c r="F29" t="n">
-        <v>970</v>
+        <v>834</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>415011208</t>
+          <t>RE-3107-4lx-96888</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1245,25 +1245,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/415011208/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx-96888/002.jpg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\415011208\002_image_415011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx-96888\2_image_RE-3107-4lx-96888.jpg</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="F30" t="n">
-        <v>895</v>
+        <v>778</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>457011208</t>
+          <t>RYv-3107-4lx</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1273,44 +1273,44 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/457011208/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RYv-3107-4lx/002.jpg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\457011208\002_image_457011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RYv-3107-4lx\2_image_RYv-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="F31" t="n">
-        <v>884</v>
+        <v>789</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>51110700108</t>
+          <t>2222-05-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51110700108/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2222-05-31/003.jpg</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\51110700108\002_image_51110700108.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\2222-05-31\3_image_2222-05-31.jpg</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1502</v>
+        <v>953</v>
       </c>
       <c r="F32" t="n">
         <v>530</v>
@@ -1319,250 +1319,250 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>512107001</t>
+          <t>51311301s</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/512107001/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/003.jpg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\512107001\002_image_512107001.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\3_image_51311301s.jpg</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1602</v>
+        <v>530</v>
       </c>
       <c r="F33" t="n">
-        <v>530</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tur-1</t>
+          <t>51411010s</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-1/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/003.jpg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-1\002_image_tur-1.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\3_image_51411010s.jpg</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>872</v>
+        <v>530</v>
       </c>
       <c r="F34" t="n">
-        <v>939</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tur-2</t>
+          <t>51411215s</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-2/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/003.jpg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-2\002_image_tur-2.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\3_image_51411215s.jpg</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1767</v>
+        <v>530</v>
       </c>
       <c r="F35" t="n">
-        <v>530</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tur-3</t>
+          <t>51411264s</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-3/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/003.jpg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-3\002_image_tur-3.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\3_image_51411264s.jpg</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>958</v>
+        <v>530</v>
       </c>
       <c r="F36" t="n">
-        <v>813</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-10</t>
+          <t>BN-BAG-62-caramel</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-10/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BAG-62-caramel/003.jpg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-10\002_image_ua-avtmt-35k-10.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\BN-BAG-62-caramel\3_image_BN-BAG-62-caramel.jpg</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>921</v>
+        <v>579</v>
       </c>
       <c r="F37" t="n">
-        <v>659</v>
+        <v>800</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-11</t>
+          <t>GARETH VT BLK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-11/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GARETH VT BLK/003.jpg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-11\002_image_ua-avtmt-35k-11.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\GARETH VT BLK\3_image_GARETH VT BLK.jpg</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>900</v>
+        <v>530</v>
       </c>
       <c r="F38" t="n">
-        <v>596</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-12</t>
+          <t>RC-0001-4lx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-12/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/003.jpg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-12\002_image_ua-avtmt-35k-12.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\3_image_RC-0001-4lx.jpg</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="F39" t="n">
-        <v>545</v>
+        <v>777</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-13</t>
+          <t>RC-3107-4lx</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>003.jpg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-13/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-3107-4lx/003.jpg</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-13\002_image_ua-avtmt-35k-13.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-3107-4lx\3_image_RC-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>925</v>
+        <v>946</v>
       </c>
       <c r="F40" t="n">
-        <v>530</v>
+        <v>630</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-14</t>
+          <t>2222-05-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-14/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2222-05-31/004.jpg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-14\002_image_ua-avtmt-35k-14.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\2222-05-31\4_image_2222-05-31.jpg</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>942</v>
+        <v>1056</v>
       </c>
       <c r="F41" t="n">
         <v>530</v>
@@ -1571,1401 +1571,2241 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-15</t>
+          <t>51411215s</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-15/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/004.jpg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-15\002_image_ua-avtmt-35k-15.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\4_image_51411215s.jpg</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>889</v>
+        <v>530</v>
       </c>
       <c r="F42" t="n">
-        <v>650</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-16</t>
+          <t>BN-BAG-62-caramel</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-16/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BAG-62-caramel/004.jpg</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-16\002_image_ua-avtmt-35k-16.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\BN-BAG-62-caramel\4_image_BN-BAG-62-caramel.jpg</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>942</v>
+        <v>579</v>
       </c>
       <c r="F43" t="n">
-        <v>550</v>
+        <v>800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-17</t>
+          <t>FA-0324-4lx</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-17/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-0324-4lx/004.jpg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-17\002_image_ua-avtmt-35k-17.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\FA-0324-4lx\4_image_FA-0324-4lx.jpg</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>932</v>
+        <v>968</v>
       </c>
       <c r="F44" t="n">
-        <v>530</v>
+        <v>710</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-18</t>
+          <t>GARETH VT BLK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-18/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GARETH VT BLK/004.jpg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-18\002_image_ua-avtmt-35k-18.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\GARETH VT BLK\4_image_GARETH VT BLK.jpg</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="F45" t="n">
-        <v>616</v>
+        <v>846</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-19</t>
+          <t>RA-3107-4lx</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-19/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RA-3107-4lx/004.jpg</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-19\002_image_ua-avtmt-35k-19.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RA-3107-4lx\4_image_RA-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>934</v>
+        <v>953</v>
       </c>
       <c r="F46" t="n">
-        <v>629</v>
+        <v>710</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-20</t>
+          <t>RC-0001-4lx</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-20/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/004.jpg</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-20\002_image_ua-avtmt-35k-20.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\4_image_RC-0001-4lx.jpg</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>925</v>
+        <v>530</v>
       </c>
       <c r="F47" t="n">
-        <v>579</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-21</t>
+          <t>RC-3107-4lx</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-21/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-3107-4lx/004.jpg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-21\002_image_ua-avtmt-35k-21.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-3107-4lx\4_image_RC-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>904</v>
+        <v>967</v>
       </c>
       <c r="F48" t="n">
-        <v>589</v>
+        <v>711</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-22</t>
+          <t>RC-8839-4lx</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>002.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-22/002.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/004.jpg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-22\002_image_ua-avtmt-35k-22.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\4_image_RC-8839-4lx.jpg</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>918</v>
+        <v>530</v>
       </c>
       <c r="F49" t="n">
-        <v>746</v>
+        <v>992</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>336201100</t>
+          <t>RE-3107-4lx</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/336201100/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx/004.jpg</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\336201100\003_image_336201100.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx\4_image_RE-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="F50" t="n">
-        <v>764</v>
+        <v>733</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>410011208</t>
+          <t>RE-3107-4lx-96888</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011208/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx-96888/004.jpg</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011208\003_image_410011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx-96888\4_image_RE-3107-4lx-96888.jpg</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="F51" t="n">
-        <v>589</v>
+        <v>736</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>410011508</t>
+          <t>RYv-3107-4lx</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>004.jpg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011508/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RYv-3107-4lx/004.jpg</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011508\003_image_410011508.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RYv-3107-4lx\4_image_RYv-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1572</v>
+        <v>969</v>
       </c>
       <c r="F52" t="n">
-        <v>530</v>
+        <v>729</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>410413701</t>
+          <t>51311301s</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410413701/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/005.jpg</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410413701\003_image_410413701.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\5_image_51311301s.jpg</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>950</v>
+        <v>530</v>
       </c>
       <c r="F53" t="n">
-        <v>904</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>415011208</t>
+          <t>51411010s</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/415011208/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/005.jpg</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\415011208\003_image_415011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\5_image_51411010s.jpg</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1389</v>
+        <v>530</v>
       </c>
       <c r="F54" t="n">
-        <v>530</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>457011208</t>
+          <t>51411264s</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/457011208/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/005.jpg</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\457011208\003_image_457011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\5_image_51411264s.jpg</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1585</v>
+        <v>530</v>
       </c>
       <c r="F55" t="n">
-        <v>530</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>51110700108</t>
+          <t>FA-0324-4lx</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51110700108/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-0324-4lx/005.jpg</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\51110700108\003_image_51110700108.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\FA-0324-4lx\5_image_FA-0324-4lx.jpg</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>937</v>
+        <v>968</v>
       </c>
       <c r="F56" t="n">
-        <v>878</v>
+        <v>659</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>512107001</t>
+          <t>GARETH VT BLK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/512107001/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GARETH VT BLK/005.jpg</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\512107001\003_image_512107001.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\GARETH VT BLK\5_image_GARETH VT BLK.jpg</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>843</v>
+        <v>1000</v>
       </c>
       <c r="F57" t="n">
-        <v>928</v>
+        <v>884</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tur-1</t>
+          <t>RA-3107-4lx</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-1/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RA-3107-4lx/005.jpg</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-1\003_image_tur-1.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RA-3107-4lx\005_image_RA-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1416</v>
+        <v>967</v>
       </c>
       <c r="F58" t="n">
-        <v>530</v>
+        <v>590</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tur-2</t>
+          <t>RC-0001-4lx</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-2/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/005.jpg</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-2\003_image_tur-2.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\5_image_RC-0001-4lx.jpg</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>951</v>
+        <v>1271</v>
       </c>
       <c r="F59" t="n">
-        <v>907</v>
+        <v>530</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tur-3</t>
+          <t>RC-3107-4lx</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-3/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-3107-4lx/005.jpg</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-3\003_image_tur-3.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-3107-4lx\5_image_RC-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1473</v>
+        <v>965</v>
       </c>
       <c r="F60" t="n">
-        <v>530</v>
+        <v>651</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-10</t>
+          <t>RC-8839-4lx</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-10/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/005.jpg</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-10\003_image_ua-avtmt-35k-10.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\5_image_RC-8839-4lx.jpg</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1010</v>
+        <v>906</v>
       </c>
       <c r="F61" t="n">
-        <v>530</v>
+        <v>941</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-11</t>
+          <t>RE-3107-4lx</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-11/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx/005.jpg</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-11\003_image_ua-avtmt-35k-11.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx\005_image_RE-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1256</v>
+        <v>968</v>
       </c>
       <c r="F62" t="n">
-        <v>530</v>
+        <v>564</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-12</t>
+          <t>RE-3107-4lx-96888</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-12/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx-96888/005.jpg</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-12\003_image_ua-avtmt-35k-12.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx-96888\5_image_RE-3107-4lx-96888.jpg</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1099</v>
+        <v>970</v>
       </c>
       <c r="F63" t="n">
-        <v>530</v>
+        <v>697</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-13</t>
+          <t>RYv-3107-4lx</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>005.jpg</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-13/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RYv-3107-4lx/005.jpg</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-13\003_image_ua-avtmt-35k-13.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RYv-3107-4lx\5_image_RYv-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1049</v>
+        <v>945</v>
       </c>
       <c r="F64" t="n">
-        <v>530</v>
+        <v>760</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-14</t>
+          <t>2222-05-31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-14/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/2222-05-31/006.jpg</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-14\003_image_ua-avtmt-35k-14.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\2222-05-31\006_image_2222-05-31.jpg</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1126</v>
+        <v>530</v>
       </c>
       <c r="F65" t="n">
-        <v>530</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-15</t>
+          <t>51311301s</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-15/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/006.jpg</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-15\003_image_ua-avtmt-35k-15.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\6_image_51311301s.jpg</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>891</v>
+        <v>530</v>
       </c>
       <c r="F66" t="n">
-        <v>566</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-16</t>
+          <t>51411010s</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-16/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/006.jpg</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-16\003_image_ua-avtmt-35k-16.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\6_image_51411010s.jpg</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1196</v>
+        <v>530</v>
       </c>
       <c r="F67" t="n">
-        <v>530</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-17</t>
+          <t>51411215s</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-17/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/006.jpg</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-17\003_image_ua-avtmt-35k-17.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\6_image_51411215s.jpg</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1320</v>
+        <v>530</v>
       </c>
       <c r="F68" t="n">
-        <v>530</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-18</t>
+          <t>51411264s</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-18/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/006.jpg</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-18\003_image_ua-avtmt-35k-18.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\6_image_51411264s.jpg</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1098</v>
+        <v>530</v>
       </c>
       <c r="F69" t="n">
-        <v>530</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-19</t>
+          <t>BN-BAG-62-caramel</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-19/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/BN-BAG-62-caramel/006.jpg</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-19\003_image_ua-avtmt-35k-19.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\BN-BAG-62-caramel\006_image_BN-BAG-62-caramel.jpg</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1032</v>
+        <v>580</v>
       </c>
       <c r="F70" t="n">
-        <v>530</v>
+        <v>800</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-20</t>
+          <t>FA-0324-4lx</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-20/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-0324-4lx/006.jpg</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-20\003_image_ua-avtmt-35k-20.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\FA-0324-4lx\6_image_FA-0324-4lx.jpg</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1205</v>
+        <v>595</v>
       </c>
       <c r="F71" t="n">
-        <v>530</v>
+        <v>852</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-21</t>
+          <t>GARETH VT BLK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-21/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/GARETH VT BLK/006.jpg</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-21\003_image_ua-avtmt-35k-21.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\GARETH VT BLK\6_image_GARETH VT BLK.jpg</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1178</v>
+        <v>1000</v>
       </c>
       <c r="F72" t="n">
-        <v>530</v>
+        <v>976</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-22</t>
+          <t>RC-0001-4lx</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>003.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-22/003.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/006.jpg</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-22\003_image_ua-avtmt-35k-22.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\6_image_RC-0001-4lx.jpg</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>916</v>
+        <v>970</v>
       </c>
       <c r="F73" t="n">
-        <v>530</v>
+        <v>728</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>336201100</t>
+          <t>RC-8839-4lx</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/336201100/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/006.jpg</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\336201100\004_image_336201100.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\6_image_RC-8839-4lx.jpg</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="F74" t="n">
-        <v>669</v>
+        <v>621</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>410011208</t>
+          <t>RE-3107-4lx-96888</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011208/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RE-3107-4lx-96888/006.jpg</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011208\004_image_410011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RE-3107-4lx-96888\006_image_RE-3107-4lx-96888.jpg</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="F75" t="n">
-        <v>643</v>
+        <v>653</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>410011508</t>
+          <t>RYv-3107-4lx</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>006.jpg</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011508/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RYv-3107-4lx/006.jpg</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011508\004_image_410011508.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RYv-3107-4lx\006_image_RYv-3107-4lx.jpg</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>951</v>
+        <v>964</v>
       </c>
       <c r="F76" t="n">
-        <v>890</v>
+        <v>601</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>410413701</t>
+          <t>51311301s</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>007.jpg</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410413701/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/007.jpg</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410413701\004_image_410413701.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\7_image_51311301s.jpg</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>911</v>
+        <v>530</v>
       </c>
       <c r="F77" t="n">
-        <v>953</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>415011208</t>
+          <t>51411010s</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>007.jpg</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/415011208/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/007.jpg</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\415011208\004_image_415011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\7_image_51411010s.jpg</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>951</v>
+        <v>530</v>
       </c>
       <c r="F78" t="n">
-        <v>815</v>
+        <v>937</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>457011208</t>
+          <t>51411215s</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>007.jpg</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/457011208/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/007.jpg</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\457011208\004_image_457011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\7_image_51411215s.jpg</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>938</v>
+        <v>530</v>
       </c>
       <c r="F79" t="n">
-        <v>916</v>
+        <v>956</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>51110700108</t>
+          <t>51411264s</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>007.jpg</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51110700108/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/007.jpg</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\51110700108\004_image_51110700108.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\7_image_51411264s.jpg</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>917</v>
+        <v>530</v>
       </c>
       <c r="F80" t="n">
-        <v>901</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>512107001</t>
+          <t>FA-0324-4lx</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>007.jpg</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/512107001/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-0324-4lx/007.jpg</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\512107001\004_image_512107001.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\FA-0324-4lx\7_image_FA-0324-4lx.jpg</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>624</v>
+        <v>884</v>
       </c>
       <c r="F81" t="n">
-        <v>955</v>
+        <v>530</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tur-1</t>
+          <t>RC-0001-4lx</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>007.jpg</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-1/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/007.jpg</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-1\004_image_tur-1.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\7_image_RC-0001-4lx.jpg</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>839</v>
+        <v>871</v>
       </c>
       <c r="F82" t="n">
-        <v>962</v>
+        <v>864</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ua-avtmt-35k-12</t>
+          <t>RC-8839-4lx</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>004.jpg</t>
+          <t>007.jpg</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/ua-avtmt-35k-12/004.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/007.jpg</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\ua-avtmt-35k-12\004_image_ua-avtmt-35k-12.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\7_image_RC-8839-4lx.jpg</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>760</v>
+        <v>970</v>
       </c>
       <c r="F83" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>336201100</t>
+          <t>51311301s</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>008.jpg</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/336201100/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/008.jpg</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\336201100\005_image_336201100.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\8_image_51311301s.jpg</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>961</v>
+        <v>530</v>
       </c>
       <c r="F84" t="n">
-        <v>645</v>
+        <v>804</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>410011208</t>
+          <t>51411010s</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>008.jpg</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/410011208/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/008.jpg</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\410011208\005_image_410011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\8_image_51411010s.jpg</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>963</v>
+        <v>530</v>
       </c>
       <c r="F85" t="n">
-        <v>825</v>
+        <v>877</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>415011208</t>
+          <t>51411215s</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>008.jpg</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/415011208/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/008.jpg</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\415011208\005_image_415011208.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\8_image_51411215s.jpg</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>938</v>
+        <v>530</v>
       </c>
       <c r="F86" t="n">
-        <v>708</v>
+        <v>924</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>51110700108</t>
+          <t>51411264s</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>008.jpg</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/51110700108/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/008.jpg</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\51110700108\005_image_51110700108.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\8_image_51411264s.jpg</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>957</v>
+        <v>530</v>
       </c>
       <c r="F87" t="n">
-        <v>893</v>
+        <v>664</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>512107001</t>
+          <t>FA-0324-4lx</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>008.jpg</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/512107001/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/FA-0324-4lx/008.jpg</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\512107001\005_image_512107001.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\FA-0324-4lx\8_image_FA-0324-4lx.jpg</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>957</v>
+        <v>530</v>
       </c>
       <c r="F88" t="n">
-        <v>534</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tur-1</t>
+          <t>RC-0001-4lx</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>005.jpg</t>
+          <t>008.jpg</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/tur-1/005.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/008.jpg</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\tur-1\005_image_tur-1.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\8_image_RC-0001-4lx.jpg</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>970</v>
+        <v>945</v>
       </c>
       <c r="F89" t="n">
-        <v>970</v>
+        <v>728</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>336201100</t>
+          <t>RC-8839-4lx</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>006.jpg</t>
+          <t>008.jpg</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/336201100/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/008.jpg</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\336201100\006_image_336201100.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\8_image_RC-8839-4lx.jpg</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>808</v>
+        <v>827</v>
       </c>
       <c r="F90" t="n">
-        <v>955</v>
+        <v>960</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>512107001</t>
+          <t>51311301s</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>006.jpg</t>
+          <t>009.jpg</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://oleks-netizen.github.io/product-images/512107001/006.jpg</t>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/009.jpg</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>C:/Users/Asus/Desktop/1 редагування2026/379 ремені/фото/6 посортовані\512107001\006_image_512107001.jpg</t>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\9_image_51311301s.jpg</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>878</v>
+        <v>530</v>
       </c>
       <c r="F91" t="n">
-        <v>915</v>
+        <v>978</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>51411010s</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/009.jpg</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\9_image_51411010s.jpg</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>530</v>
+      </c>
+      <c r="F92" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/009.jpg</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\9_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>530</v>
+      </c>
+      <c r="F93" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>51411264s</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/009.jpg</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\9_image_51411264s.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>530</v>
+      </c>
+      <c r="F94" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FA-0324-4lx</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/FA-0324-4lx/009.jpg</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\FA-0324-4lx\009_image_FA-0324-4lx.jpg</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>970</v>
+      </c>
+      <c r="F95" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>RC-0001-4lx</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/009.jpg</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\9_image_RC-0001-4lx.jpg</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>970</v>
+      </c>
+      <c r="F96" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>RC-8839-4lx</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>009.jpg</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/009.jpg</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\9_image_RC-8839-4lx.jpg</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>970</v>
+      </c>
+      <c r="F97" t="n">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>51311301s</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/010.jpg</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\10_image_51311301s.jpg</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>530</v>
+      </c>
+      <c r="F98" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>51411010s</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/010.jpg</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\10_image_51411010s.jpg</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>530</v>
+      </c>
+      <c r="F99" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/010.jpg</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\10_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>530</v>
+      </c>
+      <c r="F100" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>51411264s</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411264s/010.jpg</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411264s\010_image_51411264s.jpg</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>530</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>RC-0001-4lx</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-0001-4lx/010.jpg</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-0001-4lx\10_image_RC-0001-4lx.jpg</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>905</v>
+      </c>
+      <c r="F102" t="n">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>RC-8839-4lx</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>010.jpg</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/RC-8839-4lx/010.jpg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\RC-8839-4lx\010_image_RC-8839-4lx.jpg</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>820</v>
+      </c>
+      <c r="F103" t="n">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>51311301s</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>011.jpg</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/011.jpg</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\11_image_51311301s.jpg</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>530</v>
+      </c>
+      <c r="F104" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>51411010s</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>011.jpg</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/011.jpg</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\11_image_51411010s.jpg</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>530</v>
+      </c>
+      <c r="F105" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>011.jpg</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/011.jpg</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\11_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>530</v>
+      </c>
+      <c r="F106" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>51311301s</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>012.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/012.jpg</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\12_image_51311301s.jpg</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>530</v>
+      </c>
+      <c r="F107" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>51411010s</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>012.jpg</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/012.jpg</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\12_image_51411010s.jpg</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>530</v>
+      </c>
+      <c r="F108" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>012.jpg</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/012.jpg</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\12_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>530</v>
+      </c>
+      <c r="F109" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>51311301s</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>013.jpg</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/013.jpg</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\13_image_51311301s.jpg</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>530</v>
+      </c>
+      <c r="F110" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>51411010s</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>013.jpg</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/013.jpg</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\13_image_51411010s.jpg</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>530</v>
+      </c>
+      <c r="F111" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>013.jpg</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/013.jpg</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\13_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>530</v>
+      </c>
+      <c r="F112" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>51311301s</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>014.jpg</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/014.jpg</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\14_image_51311301s.jpg</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>530</v>
+      </c>
+      <c r="F113" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>51411010s</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>014.jpg</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411010s/014.jpg</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411010s\014_image_51411010s.jpg</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>530</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>014.jpg</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/014.jpg</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\14_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>530</v>
+      </c>
+      <c r="F115" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>51311301s</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>015.jpg</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/015.jpg</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\15_image_51311301s.jpg</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>530</v>
+      </c>
+      <c r="F116" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>015.jpg</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/015.jpg</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\15_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>530</v>
+      </c>
+      <c r="F117" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>51311301s</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>016.jpg</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/016.jpg</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\16_image_51311301s.jpg</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>530</v>
+      </c>
+      <c r="F118" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>016.jpg</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/016.jpg</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\16_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>530</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>51311301s</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>017.jpg</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51311301s/017.jpg</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51311301s\017_image_51311301s.jpg</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>530</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>51411215s</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>017.jpg</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://oleks-netizen.github.io/product-images/51411215s/017.jpg</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>C:/Users/Asus/Desktop/1 редагування2026/380/фото/6 посортовані\51411215s\017_image_51411215s.jpg</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>530</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1206</v>
       </c>
     </row>
   </sheetData>
